--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q593"/>
+  <dimension ref="A1:Q595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -36493,10 +36493,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C591" s="2" t="inlineStr">
-        <is>
-          <t>601208</t>
-        </is>
+      <c r="C591" s="2" t="n">
+        <v>601208</v>
       </c>
       <c r="D591" s="2" t="inlineStr">
         <is>
@@ -36556,10 +36554,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C592" s="2" t="inlineStr">
-        <is>
-          <t>300054</t>
-        </is>
+      <c r="C592" s="2" t="n">
+        <v>300054</v>
       </c>
       <c r="D592" s="2" t="inlineStr">
         <is>
@@ -36619,10 +36615,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C593" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C593" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D593" s="2" t="inlineStr">
         <is>
@@ -36668,6 +36662,132 @@
       <c r="Q593" s="2" t="inlineStr">
         <is>
           <t>0.72%</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B594" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C594" s="2" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
+      </c>
+      <c r="D594" s="2" t="inlineStr">
+        <is>
+          <t>鼎龙股份</t>
+        </is>
+      </c>
+      <c r="E594" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F594" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G594" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H594" s="2" t="n">
+        <v>67.98999999999999</v>
+      </c>
+      <c r="I594" s="2" t="n">
+        <v>68.59</v>
+      </c>
+      <c r="J594" s="2" t="n">
+        <v>13598</v>
+      </c>
+      <c r="K594" s="2" t="n">
+        <v>13718</v>
+      </c>
+      <c r="L594" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="M594" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N594" s="2" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="O594" s="2" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="P594" s="3" t="n">
+        <v>103.14</v>
+      </c>
+      <c r="Q594" s="2" t="inlineStr">
+        <is>
+          <t>0.76%</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B595" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户</t>
+        </is>
+      </c>
+      <c r="C595" s="2" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
+      </c>
+      <c r="D595" s="2" t="inlineStr">
+        <is>
+          <t>东材科技</t>
+        </is>
+      </c>
+      <c r="E595" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F595" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G595" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H595" s="2" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="I595" s="2" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="J595" s="2" t="n">
+        <v>4941</v>
+      </c>
+      <c r="K595" s="2" t="n">
+        <v>5010</v>
+      </c>
+      <c r="L595" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="M595" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N595" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O595" s="2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="P595" s="3" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="Q595" s="2" t="inlineStr">
+        <is>
+          <t>1.14%</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q595"/>
+  <dimension ref="A1:Q599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -36676,10 +36676,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C594" s="2" t="inlineStr">
-        <is>
-          <t>300054</t>
-        </is>
+      <c r="C594" s="2" t="n">
+        <v>300054</v>
       </c>
       <c r="D594" s="2" t="inlineStr">
         <is>
@@ -36739,10 +36737,8 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C595" s="2" t="inlineStr">
-        <is>
-          <t>601208</t>
-        </is>
+      <c r="C595" s="2" t="n">
+        <v>601208</v>
       </c>
       <c r="D595" s="2" t="inlineStr">
         <is>
@@ -36788,6 +36784,258 @@
       <c r="Q595" s="2" t="inlineStr">
         <is>
           <t>1.14%</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B596" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C596" s="2" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
+      </c>
+      <c r="D596" s="2" t="inlineStr">
+        <is>
+          <t>鼎龙股份</t>
+        </is>
+      </c>
+      <c r="E596" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F596" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G596" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H596" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I596" s="2" t="n">
+        <v>70.39</v>
+      </c>
+      <c r="J596" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K596" s="2" t="n">
+        <v>14078</v>
+      </c>
+      <c r="L596" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M596" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N596" s="2" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="O596" s="2" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="P596" s="4" t="n">
+        <v>-12.04</v>
+      </c>
+      <c r="Q596" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B597" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C597" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D597" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E597" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F597" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G597" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H597" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I597" s="2" t="n">
+        <v>199.89</v>
+      </c>
+      <c r="J597" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K597" s="2" t="n">
+        <v>39978</v>
+      </c>
+      <c r="L597" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M597" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N597" s="2" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="O597" s="2" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="P597" s="4" t="n">
+        <v>-24.99</v>
+      </c>
+      <c r="Q597" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B598" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C598" s="2" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
+      </c>
+      <c r="D598" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="E598" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F598" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G598" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H598" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I598" s="2" t="n">
+        <v>304</v>
+      </c>
+      <c r="J598" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K598" s="2" t="n">
+        <v>30400</v>
+      </c>
+      <c r="L598" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M598" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N598" s="2" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="O598" s="2" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="P598" s="4" t="n">
+        <v>-20.2</v>
+      </c>
+      <c r="Q598" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B599" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C599" s="2" t="inlineStr">
+        <is>
+          <t>603228</t>
+        </is>
+      </c>
+      <c r="D599" s="2" t="inlineStr">
+        <is>
+          <t>景旺电子</t>
+        </is>
+      </c>
+      <c r="E599" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F599" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G599" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H599" s="2" t="n">
+        <v>105.22</v>
+      </c>
+      <c r="I599" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J599" s="2" t="n">
+        <v>31566</v>
+      </c>
+      <c r="K599" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L599" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M599" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N599" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O599" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P599" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q599" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q599"/>
+  <dimension ref="A1:Q600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -36798,10 +36798,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C596" s="2" t="inlineStr">
-        <is>
-          <t>300054</t>
-        </is>
+      <c r="C596" s="2" t="n">
+        <v>300054</v>
       </c>
       <c r="D596" s="2" t="inlineStr">
         <is>
@@ -36861,10 +36859,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C597" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C597" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D597" s="2" t="inlineStr">
         <is>
@@ -36924,10 +36920,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C598" s="2" t="inlineStr">
-        <is>
-          <t>300750</t>
-        </is>
+      <c r="C598" s="2" t="n">
+        <v>300750</v>
       </c>
       <c r="D598" s="2" t="inlineStr">
         <is>
@@ -36987,10 +36981,8 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C599" s="2" t="inlineStr">
-        <is>
-          <t>603228</t>
-        </is>
+      <c r="C599" s="2" t="n">
+        <v>603228</v>
       </c>
       <c r="D599" s="2" t="inlineStr">
         <is>
@@ -37034,6 +37026,69 @@
         <v>-5</v>
       </c>
       <c r="Q599" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B600" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C600" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D600" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E600" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F600" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G600" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H600" s="2" t="n">
+        <v>197.11</v>
+      </c>
+      <c r="I600" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J600" s="2" t="n">
+        <v>39422</v>
+      </c>
+      <c r="K600" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L600" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M600" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N600" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O600" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P600" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q600" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
         </is>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q600"/>
+  <dimension ref="A1:Q604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -37042,10 +37042,8 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C600" s="2" t="inlineStr">
-        <is>
-          <t>688008</t>
-        </is>
+      <c r="C600" s="2" t="n">
+        <v>688008</v>
       </c>
       <c r="D600" s="2" t="inlineStr">
         <is>
@@ -37089,6 +37087,258 @@
         <v>-5</v>
       </c>
       <c r="Q600" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B601" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C601" s="2" t="inlineStr">
+        <is>
+          <t>002916</t>
+        </is>
+      </c>
+      <c r="D601" s="2" t="inlineStr">
+        <is>
+          <t>深南电路</t>
+        </is>
+      </c>
+      <c r="E601" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F601" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G601" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H601" s="2" t="n">
+        <v>386.29</v>
+      </c>
+      <c r="I601" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J601" s="2" t="n">
+        <v>38629</v>
+      </c>
+      <c r="K601" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L601" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M601" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N601" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O601" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P601" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q601" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B602" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C602" s="2" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D602" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E602" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F602" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G602" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H602" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I602" s="2" t="n">
+        <v>199.99</v>
+      </c>
+      <c r="J602" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K602" s="2" t="n">
+        <v>39998</v>
+      </c>
+      <c r="L602" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M602" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N602" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="O602" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="P602" s="4" t="n">
+        <v>-25</v>
+      </c>
+      <c r="Q602" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B603" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C603" s="2" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D603" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E603" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F603" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G603" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H603" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I603" s="2" t="n">
+        <v>42.89</v>
+      </c>
+      <c r="J603" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K603" s="2" t="n">
+        <v>21445</v>
+      </c>
+      <c r="L603" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M603" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N603" s="2" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="O603" s="2" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="P603" s="4" t="n">
+        <v>-15.72</v>
+      </c>
+      <c r="Q603" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B604" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C604" s="2" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D604" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E604" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F604" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G604" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H604" s="2" t="n">
+        <v>241.56</v>
+      </c>
+      <c r="I604" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J604" s="2" t="n">
+        <v>48312</v>
+      </c>
+      <c r="K604" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L604" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M604" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N604" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O604" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P604" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q604" s="2" t="inlineStr">
         <is>
           <t>⚠️仅买入未平仓</t>
         </is>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -65,7 +65,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -77,6 +77,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -564,8 +567,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>300394</v>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -625,8 +630,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>688025</v>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -686,8 +693,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>688041</v>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -747,8 +756,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>688503</v>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>688503</t>
+        </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -808,8 +819,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>300394</v>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -869,8 +882,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
-        <v>300014</v>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>300014</t>
+        </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -930,8 +945,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>688503</v>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>688503</t>
+        </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -991,8 +1008,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>688025</v>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -1052,8 +1071,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>300750</v>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -1113,8 +1134,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>2222</v>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -1174,8 +1197,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>603920</v>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>603920</t>
+        </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -1235,8 +1260,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>300394</v>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -1296,8 +1323,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>688041</v>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -1357,8 +1386,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>688041</v>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -1418,8 +1449,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
-        <v>300394</v>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -1479,8 +1512,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>688041</v>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -1540,8 +1575,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
-        <v>688503</v>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>688503</t>
+        </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -1601,8 +1638,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n">
-        <v>300054</v>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -1662,8 +1701,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>2594</v>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
@@ -1723,8 +1764,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n">
-        <v>688503</v>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>688503</t>
+        </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
@@ -1784,8 +1827,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n">
-        <v>300502</v>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -1845,8 +1890,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>688025</v>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
@@ -1906,8 +1953,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>2594</v>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
@@ -1967,8 +2016,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>688041</v>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
@@ -2028,8 +2079,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
-        <v>300394</v>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
@@ -2089,8 +2142,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n">
-        <v>300750</v>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
@@ -2150,8 +2205,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n">
-        <v>688062</v>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>688062</t>
+        </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
@@ -2211,8 +2268,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>300750</v>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
@@ -2272,8 +2331,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>300502</v>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
@@ -2333,8 +2394,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>300308</v>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
@@ -2394,8 +2457,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>688041</v>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
@@ -2455,8 +2520,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n">
-        <v>688503</v>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>688503</t>
+        </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
@@ -2516,8 +2583,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n">
-        <v>300450</v>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>300450</t>
+        </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
@@ -2577,8 +2646,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>300502</v>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
@@ -2638,8 +2709,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>300750</v>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
@@ -2699,8 +2772,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>688041</v>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
@@ -2760,8 +2835,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>300394</v>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
@@ -2821,8 +2898,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>2594</v>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
@@ -2882,8 +2961,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n">
-        <v>688503</v>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>688503</t>
+        </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
@@ -2943,8 +3024,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n">
-        <v>300394</v>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
@@ -3004,8 +3087,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n">
-        <v>688041</v>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
@@ -3065,8 +3150,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n">
-        <v>2222</v>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
@@ -3126,8 +3213,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n">
-        <v>300750</v>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
@@ -3187,8 +3276,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n">
-        <v>300750</v>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
@@ -3248,8 +3339,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
-        <v>688503</v>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>688503</t>
+        </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
@@ -3309,8 +3402,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>688041</v>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
@@ -3370,8 +3465,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>688503</v>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>688503</t>
+        </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
@@ -3431,8 +3528,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
-        <v>300054</v>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
@@ -3492,8 +3591,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n">
-        <v>2222</v>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
@@ -3553,8 +3654,10 @@
           <t>平安账户</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>688778</v>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>688778</t>
+        </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
@@ -3614,8 +3717,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>2436</v>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
@@ -3675,8 +3780,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n">
-        <v>301183</v>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>301183</t>
+        </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
@@ -3736,8 +3843,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n">
-        <v>300394</v>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
@@ -3797,8 +3906,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n">
-        <v>300450</v>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>300450</t>
+        </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
@@ -3858,8 +3969,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n">
-        <v>688041</v>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
@@ -3919,8 +4032,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>600498</v>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
@@ -3980,8 +4095,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n">
-        <v>2594</v>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
@@ -4041,8 +4158,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>300750</v>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
@@ -4102,8 +4221,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n">
-        <v>688041</v>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
@@ -4163,8 +4284,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n">
-        <v>988</v>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>000988</t>
+        </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
@@ -4224,8 +4347,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n">
-        <v>2594</v>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
@@ -4285,8 +4410,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C63" s="2" t="n">
-        <v>688041</v>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
@@ -4346,8 +4473,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n">
-        <v>2222</v>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
@@ -4407,8 +4536,10 @@
           <t>平安账户</t>
         </is>
       </c>
-      <c r="C65" s="2" t="n">
-        <v>601208</v>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
@@ -4468,8 +4599,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n">
-        <v>300308</v>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
@@ -4529,8 +4662,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n">
-        <v>300502</v>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
@@ -4590,8 +4725,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C68" s="2" t="n">
-        <v>688041</v>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
@@ -4651,8 +4788,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n">
-        <v>688062</v>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>688062</t>
+        </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
@@ -4712,8 +4851,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C70" s="2" t="n">
-        <v>300750</v>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
@@ -4773,8 +4914,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C71" s="2" t="n">
-        <v>300750</v>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
@@ -4834,8 +4977,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n">
-        <v>601899</v>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>601899</t>
+        </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
@@ -4895,8 +5040,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C73" s="2" t="n">
-        <v>2222</v>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
@@ -4956,8 +5103,10 @@
           <t>跨账户(两融账户+手机账户)</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>300502</v>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
@@ -5017,8 +5166,10 @@
           <t>跨账户(两融账户+手机账户)</t>
         </is>
       </c>
-      <c r="C75" s="2" t="n">
-        <v>300394</v>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
@@ -5078,8 +5229,10 @@
           <t>跨账户(两融账户+手机账户)</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n">
-        <v>300394</v>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
@@ -5139,8 +5292,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n">
-        <v>300750</v>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
@@ -5200,8 +5355,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C78" s="2" t="n">
-        <v>600259</v>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>600259</t>
+        </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
@@ -5261,8 +5418,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n">
-        <v>2222</v>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
@@ -5322,8 +5481,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n">
-        <v>300308</v>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
@@ -5383,8 +5544,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C81" s="2" t="n">
-        <v>300394</v>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
@@ -5444,8 +5607,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C82" s="2" t="n">
-        <v>831</v>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
@@ -5505,8 +5670,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C83" s="2" t="n">
-        <v>123269</v>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>123269</t>
+        </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
@@ -5566,8 +5733,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C84" s="2" t="n">
-        <v>688041</v>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
@@ -5627,8 +5796,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n">
-        <v>300014</v>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>300014</t>
+        </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
@@ -5688,8 +5859,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>300450</v>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>300450</t>
+        </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
@@ -5749,8 +5922,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C87" s="2" t="n">
-        <v>2156</v>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
@@ -5810,8 +5985,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n">
-        <v>688025</v>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
@@ -5871,8 +6048,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C89" s="2" t="n">
-        <v>2837</v>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>002837</t>
+        </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
@@ -5932,8 +6111,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>2222</v>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
@@ -5993,8 +6174,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C91" s="2" t="n">
-        <v>688041</v>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
@@ -6054,8 +6237,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n">
-        <v>688041</v>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
@@ -6115,8 +6300,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C93" s="2" t="n">
-        <v>300502</v>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
@@ -6176,8 +6363,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C94" s="2" t="n">
-        <v>300502</v>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
@@ -6237,8 +6426,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C95" s="2" t="n">
-        <v>831</v>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
@@ -6298,8 +6489,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n">
-        <v>988</v>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>000988</t>
+        </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
@@ -6359,8 +6552,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C97" s="2" t="n">
-        <v>688062</v>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>688062</t>
+        </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
@@ -6420,8 +6615,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n">
-        <v>601208</v>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
@@ -6481,8 +6678,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>300394</v>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
@@ -6542,8 +6741,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n">
-        <v>2436</v>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
@@ -6603,8 +6804,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C101" s="2" t="n">
-        <v>2436</v>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
@@ -6664,8 +6867,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C102" s="2" t="n">
-        <v>600498</v>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
@@ -6725,8 +6930,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C103" s="2" t="n">
-        <v>603920</v>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>603920</t>
+        </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
@@ -6786,8 +6993,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C104" s="2" t="n">
-        <v>688025</v>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
@@ -6847,8 +7056,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C105" s="2" t="n">
-        <v>688041</v>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
@@ -6908,8 +7119,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n">
-        <v>2222</v>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
@@ -6969,8 +7182,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n">
-        <v>2222</v>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
@@ -7030,8 +7245,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C108" s="2" t="n">
-        <v>688503</v>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>688503</t>
+        </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
@@ -7091,8 +7308,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>300502</v>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
@@ -7152,8 +7371,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C110" s="2" t="n">
-        <v>300502</v>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
@@ -7213,8 +7434,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C111" s="2" t="n">
-        <v>2222</v>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
@@ -7274,8 +7497,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C112" s="2" t="n">
-        <v>688025</v>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
@@ -7335,8 +7560,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C113" s="2" t="n">
-        <v>688025</v>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
@@ -7396,8 +7623,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n">
-        <v>603881</v>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>603881</t>
+        </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
@@ -7457,8 +7686,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n">
-        <v>688041</v>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
@@ -7518,8 +7749,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n">
-        <v>988</v>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>000988</t>
+        </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
@@ -7579,8 +7812,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n">
-        <v>2384</v>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>002384</t>
+        </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
@@ -7640,8 +7875,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C118" s="2" t="n">
-        <v>512000</v>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>512000</t>
+        </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
@@ -7701,8 +7938,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C119" s="2" t="n">
-        <v>600498</v>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
@@ -7762,8 +8001,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C120" s="2" t="n">
-        <v>601899</v>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>601899</t>
+        </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
@@ -7823,8 +8064,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C121" s="2" t="n">
-        <v>300450</v>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>300450</t>
+        </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
@@ -7884,8 +8127,10 @@
           <t>跨账户(两融账户+手机账户)</t>
         </is>
       </c>
-      <c r="C122" s="2" t="n">
-        <v>688503</v>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>688503</t>
+        </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
@@ -7945,8 +8190,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n">
-        <v>300054</v>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
@@ -8006,8 +8253,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C124" s="2" t="n">
-        <v>688041</v>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
@@ -8067,8 +8316,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n">
-        <v>688041</v>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
@@ -8128,8 +8379,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C126" s="2" t="n">
-        <v>300308</v>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
@@ -8189,8 +8442,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n">
-        <v>2156</v>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
@@ -8250,8 +8505,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C128" s="2" t="n">
-        <v>2156</v>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
@@ -8311,8 +8568,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C129" s="2" t="n">
-        <v>688025</v>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
@@ -8372,8 +8631,10 @@
           <t>跨账户(两融账户+手机账户)</t>
         </is>
       </c>
-      <c r="C130" s="2" t="n">
-        <v>300502</v>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
@@ -8433,8 +8694,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C131" s="2" t="n">
-        <v>688035</v>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>688035</t>
+        </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
@@ -8494,8 +8757,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C132" s="2" t="n">
-        <v>688062</v>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>688062</t>
+        </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
@@ -8555,8 +8820,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C133" s="2" t="n">
-        <v>688025</v>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
@@ -8616,8 +8883,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C134" s="2" t="n">
-        <v>688025</v>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
@@ -8677,8 +8946,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C135" s="2" t="n">
-        <v>603920</v>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>603920</t>
+        </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
@@ -8738,8 +9009,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C136" s="2" t="n">
-        <v>688041</v>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
@@ -8799,8 +9072,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C137" s="2" t="n">
-        <v>688041</v>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
@@ -8860,8 +9135,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C138" s="2" t="n">
-        <v>300502</v>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
@@ -8921,8 +9198,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C139" s="2" t="n">
-        <v>300054</v>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
@@ -8982,8 +9261,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C140" s="2" t="n">
-        <v>2222</v>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
@@ -9043,8 +9324,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C141" s="2" t="n">
-        <v>688025</v>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
@@ -9104,8 +9387,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C142" s="2" t="n">
-        <v>688025</v>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
@@ -9165,8 +9450,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C143" s="2" t="n">
-        <v>600498</v>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
@@ -9226,8 +9513,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C144" s="2" t="n">
-        <v>688035</v>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>688035</t>
+        </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
@@ -9287,8 +9576,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C145" s="2" t="n">
-        <v>2436</v>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
@@ -9348,8 +9639,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C146" s="2" t="n">
-        <v>300450</v>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>300450</t>
+        </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
@@ -9409,8 +9702,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C147" s="2" t="n">
-        <v>300308</v>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
@@ -9470,8 +9765,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C148" s="2" t="n">
-        <v>600498</v>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
@@ -9531,8 +9828,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C149" s="2" t="n">
-        <v>688035</v>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>688035</t>
+        </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
@@ -9592,8 +9891,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C150" s="2" t="n">
-        <v>688025</v>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
@@ -9653,8 +9954,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C151" s="2" t="n">
-        <v>688025</v>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
@@ -9714,8 +10017,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C152" s="2" t="n">
-        <v>300750</v>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
@@ -9775,8 +10080,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C153" s="2" t="n">
-        <v>2222</v>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
@@ -9836,8 +10143,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C154" s="2" t="n">
-        <v>300502</v>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
@@ -9897,8 +10206,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C155" s="2" t="n">
-        <v>688041</v>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
@@ -9958,8 +10269,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C156" s="2" t="n">
-        <v>688041</v>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
@@ -10019,8 +10332,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C157" s="2" t="n">
-        <v>300502</v>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
@@ -10080,8 +10395,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C158" s="2" t="n">
-        <v>300502</v>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
@@ -10141,8 +10458,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C159" s="2" t="n">
-        <v>688503</v>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>688503</t>
+        </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
@@ -10202,8 +10521,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C160" s="2" t="n">
-        <v>300014</v>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>300014</t>
+        </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
@@ -10263,8 +10584,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C161" s="2" t="n">
-        <v>300308</v>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
@@ -10324,8 +10647,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C162" s="2" t="n">
-        <v>688025</v>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
@@ -10385,8 +10710,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C163" s="2" t="n">
-        <v>300660</v>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>300660</t>
+        </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
@@ -10446,8 +10773,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C164" s="2" t="n">
-        <v>688041</v>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
@@ -10507,8 +10836,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C165" s="2" t="n">
-        <v>2156</v>
+      <c r="C165" s="5" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
@@ -10568,8 +10899,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C166" s="2" t="n">
-        <v>601208</v>
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
@@ -10629,8 +10962,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C167" s="2" t="n">
-        <v>300502</v>
+      <c r="C167" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
@@ -10690,8 +11025,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C168" s="2" t="n">
-        <v>300308</v>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
@@ -10751,8 +11088,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C169" s="2" t="n">
-        <v>688062</v>
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>688062</t>
+        </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
@@ -10812,8 +11151,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C170" s="2" t="n">
-        <v>2436</v>
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
@@ -10873,8 +11214,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C171" s="2" t="n">
-        <v>600498</v>
+      <c r="C171" s="5" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
@@ -10934,8 +11277,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C172" s="2" t="n">
-        <v>688025</v>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
@@ -10995,8 +11340,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C173" s="2" t="n">
-        <v>688041</v>
+      <c r="C173" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
@@ -11056,8 +11403,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C174" s="2" t="n">
-        <v>688041</v>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
@@ -11117,8 +11466,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C175" s="2" t="n">
-        <v>2436</v>
+      <c r="C175" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
@@ -11178,8 +11529,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C176" s="2" t="n">
-        <v>688503</v>
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t>688503</t>
+        </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
@@ -11239,8 +11592,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C177" s="2" t="n">
-        <v>688503</v>
+      <c r="C177" s="5" t="inlineStr">
+        <is>
+          <t>688503</t>
+        </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
@@ -11300,8 +11655,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C178" s="2" t="n">
-        <v>300502</v>
+      <c r="C178" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
@@ -11361,8 +11718,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C179" s="2" t="n">
-        <v>300308</v>
+      <c r="C179" s="5" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
@@ -11422,8 +11781,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C180" s="2" t="n">
-        <v>688025</v>
+      <c r="C180" s="5" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
@@ -11483,8 +11844,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C181" s="2" t="n">
-        <v>688041</v>
+      <c r="C181" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
@@ -11544,8 +11907,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C182" s="2" t="n">
-        <v>688035</v>
+      <c r="C182" s="5" t="inlineStr">
+        <is>
+          <t>688035</t>
+        </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
@@ -11605,8 +11970,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C183" s="2" t="n">
-        <v>688035</v>
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>688035</t>
+        </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
@@ -11666,8 +12033,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C184" s="2" t="n">
-        <v>600498</v>
+      <c r="C184" s="5" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
@@ -11727,8 +12096,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C185" s="2" t="n">
-        <v>300308</v>
+      <c r="C185" s="5" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
@@ -11788,8 +12159,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C186" s="2" t="n">
-        <v>688025</v>
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
@@ -11849,8 +12222,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C187" s="2" t="n">
-        <v>688041</v>
+      <c r="C187" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
@@ -11910,8 +12285,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C188" s="2" t="n">
-        <v>300750</v>
+      <c r="C188" s="5" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
@@ -11971,8 +12348,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C189" s="2" t="n">
-        <v>688041</v>
+      <c r="C189" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
@@ -12032,8 +12411,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C190" s="2" t="n">
-        <v>688025</v>
+      <c r="C190" s="5" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
@@ -12093,8 +12474,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C191" s="2" t="n">
-        <v>688035</v>
+      <c r="C191" s="5" t="inlineStr">
+        <is>
+          <t>688035</t>
+        </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
@@ -12154,8 +12537,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C192" s="2" t="n">
-        <v>2222</v>
+      <c r="C192" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
@@ -12215,8 +12600,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C193" s="2" t="n">
-        <v>688503</v>
+      <c r="C193" s="5" t="inlineStr">
+        <is>
+          <t>688503</t>
+        </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
@@ -12276,8 +12663,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C194" s="2" t="n">
-        <v>300308</v>
+      <c r="C194" s="5" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
@@ -12337,8 +12726,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C195" s="2" t="n">
-        <v>2436</v>
+      <c r="C195" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
@@ -12398,8 +12789,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C196" s="2" t="n">
-        <v>300308</v>
+      <c r="C196" s="5" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
@@ -12459,8 +12852,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C197" s="2" t="n">
-        <v>300502</v>
+      <c r="C197" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
@@ -12520,8 +12915,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C198" s="2" t="n">
-        <v>300502</v>
+      <c r="C198" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
@@ -12581,8 +12978,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C199" s="2" t="n">
-        <v>2436</v>
+      <c r="C199" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
@@ -12642,8 +13041,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C200" s="2" t="n">
-        <v>300394</v>
+      <c r="C200" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
@@ -12703,8 +13104,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C201" s="2" t="n">
-        <v>688025</v>
+      <c r="C201" s="5" t="inlineStr">
+        <is>
+          <t>688025</t>
+        </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
@@ -12764,8 +13167,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C202" s="2" t="n">
-        <v>688041</v>
+      <c r="C202" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
@@ -12825,8 +13230,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C203" s="2" t="n">
-        <v>688041</v>
+      <c r="C203" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
@@ -12886,8 +13293,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C204" s="2" t="n">
-        <v>300502</v>
+      <c r="C204" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
@@ -12947,8 +13356,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C205" s="2" t="n">
-        <v>603920</v>
+      <c r="C205" s="5" t="inlineStr">
+        <is>
+          <t>603920</t>
+        </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
@@ -13008,8 +13419,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C206" s="2" t="n">
-        <v>2436</v>
+      <c r="C206" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
@@ -13069,8 +13482,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C207" s="2" t="n">
-        <v>2594</v>
+      <c r="C207" s="5" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
@@ -13130,8 +13545,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C208" s="2" t="n">
-        <v>688008</v>
+      <c r="C208" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
@@ -13191,8 +13608,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C209" s="2" t="n">
-        <v>688008</v>
+      <c r="C209" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
@@ -13252,8 +13671,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C210" s="2" t="n">
-        <v>2222</v>
+      <c r="C210" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
@@ -13313,8 +13734,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C211" s="2" t="n">
-        <v>688041</v>
+      <c r="C211" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
@@ -13374,8 +13797,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C212" s="2" t="n">
-        <v>2222</v>
+      <c r="C212" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
@@ -13435,8 +13860,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C213" s="2" t="n">
-        <v>2594</v>
+      <c r="C213" s="5" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
@@ -13496,8 +13923,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C214" s="2" t="n">
-        <v>688008</v>
+      <c r="C214" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
@@ -13557,8 +13986,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C215" s="2" t="n">
-        <v>603920</v>
+      <c r="C215" s="5" t="inlineStr">
+        <is>
+          <t>603920</t>
+        </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
@@ -13618,8 +14049,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C216" s="2" t="n">
-        <v>688062</v>
+      <c r="C216" s="5" t="inlineStr">
+        <is>
+          <t>688062</t>
+        </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
@@ -13679,8 +14112,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C217" s="2" t="n">
-        <v>2436</v>
+      <c r="C217" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
@@ -13740,8 +14175,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C218" s="2" t="n">
-        <v>2436</v>
+      <c r="C218" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
@@ -13801,8 +14238,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C219" s="2" t="n">
-        <v>300394</v>
+      <c r="C219" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
@@ -13862,8 +14301,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C220" s="2" t="n">
-        <v>300450</v>
+      <c r="C220" s="5" t="inlineStr">
+        <is>
+          <t>300450</t>
+        </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
@@ -13923,8 +14364,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C221" s="2" t="n">
-        <v>300502</v>
+      <c r="C221" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
@@ -13984,8 +14427,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C222" s="2" t="n">
-        <v>300502</v>
+      <c r="C222" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
@@ -14045,8 +14490,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C223" s="2" t="n">
-        <v>601899</v>
+      <c r="C223" s="5" t="inlineStr">
+        <is>
+          <t>601899</t>
+        </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
@@ -14106,8 +14553,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C224" s="2" t="n">
-        <v>2222</v>
+      <c r="C224" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
@@ -14167,8 +14616,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C225" s="2" t="n">
-        <v>988</v>
+      <c r="C225" s="5" t="inlineStr">
+        <is>
+          <t>000988</t>
+        </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
@@ -14228,8 +14679,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C226" s="2" t="n">
-        <v>2594</v>
+      <c r="C226" s="5" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
@@ -14289,8 +14742,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C227" s="2" t="n">
-        <v>688041</v>
+      <c r="C227" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
@@ -14350,8 +14805,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C228" s="2" t="n">
-        <v>688008</v>
+      <c r="C228" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
@@ -14411,8 +14868,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C229" s="2" t="n">
-        <v>300394</v>
+      <c r="C229" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
@@ -14472,8 +14931,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C230" s="2" t="n">
-        <v>300502</v>
+      <c r="C230" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
@@ -14533,8 +14994,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C231" s="2" t="n">
-        <v>300054</v>
+      <c r="C231" s="5" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
@@ -14594,8 +15057,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C232" s="2" t="n">
-        <v>688008</v>
+      <c r="C232" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
@@ -14655,8 +15120,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C233" s="2" t="n">
-        <v>600498</v>
+      <c r="C233" s="5" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
@@ -14716,8 +15183,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C234" s="2" t="n">
-        <v>300308</v>
+      <c r="C234" s="5" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
@@ -14777,8 +15246,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C235" s="2" t="n">
-        <v>688503</v>
+      <c r="C235" s="5" t="inlineStr">
+        <is>
+          <t>688503</t>
+        </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
@@ -14838,8 +15309,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C236" s="2" t="n">
-        <v>601208</v>
+      <c r="C236" s="5" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
@@ -14899,8 +15372,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C237" s="2" t="n">
-        <v>2222</v>
+      <c r="C237" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
@@ -14960,8 +15435,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C238" s="2" t="n">
-        <v>688041</v>
+      <c r="C238" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
@@ -15021,8 +15498,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C239" s="2" t="n">
-        <v>688041</v>
+      <c r="C239" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
@@ -15082,8 +15561,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C240" s="2" t="n">
-        <v>601208</v>
+      <c r="C240" s="5" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
@@ -15143,8 +15624,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C241" s="2" t="n">
-        <v>601208</v>
+      <c r="C241" s="5" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
@@ -15204,8 +15687,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C242" s="2" t="n">
-        <v>2436</v>
+      <c r="C242" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
@@ -15265,8 +15750,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C243" s="2" t="n">
-        <v>2384</v>
+      <c r="C243" s="5" t="inlineStr">
+        <is>
+          <t>002384</t>
+        </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
@@ -15326,8 +15813,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C244" s="2" t="n">
-        <v>988</v>
+      <c r="C244" s="5" t="inlineStr">
+        <is>
+          <t>000988</t>
+        </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
@@ -15387,8 +15876,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C245" s="2" t="n">
-        <v>300502</v>
+      <c r="C245" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
@@ -15448,8 +15939,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C246" s="2" t="n">
-        <v>600498</v>
+      <c r="C246" s="5" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
@@ -15509,8 +16002,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C247" s="2" t="n">
-        <v>688008</v>
+      <c r="C247" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
@@ -15570,8 +16065,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C248" s="2" t="n">
-        <v>688008</v>
+      <c r="C248" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
@@ -15631,8 +16128,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C249" s="2" t="n">
-        <v>300308</v>
+      <c r="C249" s="5" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
@@ -15692,8 +16191,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C250" s="2" t="n">
-        <v>603920</v>
+      <c r="C250" s="5" t="inlineStr">
+        <is>
+          <t>603920</t>
+        </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
@@ -15753,8 +16254,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C251" s="2" t="n">
-        <v>300054</v>
+      <c r="C251" s="5" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
@@ -15814,8 +16317,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C252" s="2" t="n">
-        <v>300450</v>
+      <c r="C252" s="5" t="inlineStr">
+        <is>
+          <t>300450</t>
+        </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
@@ -15875,8 +16380,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C253" s="2" t="n">
-        <v>2222</v>
+      <c r="C253" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
@@ -15936,8 +16443,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C254" s="2" t="n">
-        <v>2436</v>
+      <c r="C254" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
@@ -15997,8 +16506,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C255" s="2" t="n">
-        <v>2436</v>
+      <c r="C255" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
@@ -16058,8 +16569,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C256" s="2" t="n">
-        <v>688008</v>
+      <c r="C256" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
@@ -16119,8 +16632,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C257" s="2" t="n">
-        <v>2922</v>
+      <c r="C257" s="5" t="inlineStr">
+        <is>
+          <t>002922</t>
+        </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
@@ -16180,8 +16695,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C258" s="2" t="n">
-        <v>300274</v>
+      <c r="C258" s="5" t="inlineStr">
+        <is>
+          <t>300274</t>
+        </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
@@ -16241,8 +16758,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C259" s="2" t="n">
-        <v>300054</v>
+      <c r="C259" s="5" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
@@ -16302,8 +16821,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C260" s="2" t="n">
-        <v>300308</v>
+      <c r="C260" s="5" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
@@ -16363,8 +16884,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C261" s="2" t="n">
-        <v>300502</v>
+      <c r="C261" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
@@ -16424,8 +16947,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C262" s="2" t="n">
-        <v>688041</v>
+      <c r="C262" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
@@ -16485,8 +17010,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C263" s="2" t="n">
-        <v>688041</v>
+      <c r="C263" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
@@ -16546,8 +17073,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C264" s="2" t="n">
-        <v>2594</v>
+      <c r="C264" s="5" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
@@ -16607,8 +17136,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C265" s="2" t="n">
-        <v>600259</v>
+      <c r="C265" s="5" t="inlineStr">
+        <is>
+          <t>600259</t>
+        </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
@@ -16668,8 +17199,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C266" s="2" t="n">
-        <v>601208</v>
+      <c r="C266" s="5" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
@@ -16729,8 +17262,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C267" s="2" t="n">
-        <v>688008</v>
+      <c r="C267" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
@@ -16790,8 +17325,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C268" s="2" t="n">
-        <v>300394</v>
+      <c r="C268" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
@@ -16851,8 +17388,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C269" s="2" t="n">
-        <v>300394</v>
+      <c r="C269" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
@@ -16912,8 +17451,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C270" s="2" t="n">
-        <v>988</v>
+      <c r="C270" s="5" t="inlineStr">
+        <is>
+          <t>000988</t>
+        </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
@@ -16973,8 +17514,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C271" s="2" t="n">
-        <v>300308</v>
+      <c r="C271" s="5" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
@@ -17034,8 +17577,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C272" s="2" t="n">
-        <v>300502</v>
+      <c r="C272" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
@@ -17095,8 +17640,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C273" s="2" t="n">
-        <v>600259</v>
+      <c r="C273" s="5" t="inlineStr">
+        <is>
+          <t>600259</t>
+        </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
@@ -17156,8 +17703,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C274" s="2" t="n">
-        <v>300502</v>
+      <c r="C274" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
@@ -17217,8 +17766,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C275" s="2" t="n">
-        <v>688503</v>
+      <c r="C275" s="5" t="inlineStr">
+        <is>
+          <t>688503</t>
+        </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
@@ -17278,8 +17829,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C276" s="2" t="n">
-        <v>300516</v>
+      <c r="C276" s="5" t="inlineStr">
+        <is>
+          <t>300516</t>
+        </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
@@ -17339,8 +17892,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C277" s="2" t="n">
-        <v>300274</v>
+      <c r="C277" s="5" t="inlineStr">
+        <is>
+          <t>300274</t>
+        </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
@@ -17400,8 +17955,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C278" s="2" t="n">
-        <v>688008</v>
+      <c r="C278" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
@@ -17461,8 +18018,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C279" s="2" t="n">
-        <v>688008</v>
+      <c r="C279" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
@@ -17522,8 +18081,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C280" s="2" t="n">
-        <v>2922</v>
+      <c r="C280" s="5" t="inlineStr">
+        <is>
+          <t>002922</t>
+        </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
@@ -17583,8 +18144,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C281" s="2" t="n">
-        <v>300548</v>
+      <c r="C281" s="5" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
@@ -17644,8 +18207,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C282" s="2" t="n">
-        <v>988</v>
+      <c r="C282" s="5" t="inlineStr">
+        <is>
+          <t>000988</t>
+        </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
@@ -17705,8 +18270,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C283" s="2" t="n">
-        <v>300054</v>
+      <c r="C283" s="5" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
@@ -17766,8 +18333,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C284" s="2" t="n">
-        <v>600498</v>
+      <c r="C284" s="5" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
@@ -17827,8 +18396,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C285" s="2" t="n">
-        <v>2156</v>
+      <c r="C285" s="5" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
@@ -17888,8 +18459,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C286" s="2" t="n">
-        <v>2594</v>
+      <c r="C286" s="5" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
@@ -17949,8 +18522,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C287" s="2" t="n">
-        <v>688041</v>
+      <c r="C287" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
@@ -18010,8 +18585,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C288" s="2" t="n">
-        <v>601208</v>
+      <c r="C288" s="5" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
@@ -18071,8 +18648,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C289" s="2" t="n">
-        <v>21</v>
+      <c r="C289" s="5" t="inlineStr">
+        <is>
+          <t>000021</t>
+        </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
@@ -18132,8 +18711,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C290" s="2" t="n">
-        <v>300394</v>
+      <c r="C290" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
@@ -18193,8 +18774,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C291" s="2" t="n">
-        <v>300394</v>
+      <c r="C291" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
@@ -18254,8 +18837,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C292" s="2" t="n">
-        <v>688676</v>
+      <c r="C292" s="5" t="inlineStr">
+        <is>
+          <t>688676</t>
+        </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
@@ -18315,8 +18900,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C293" s="2" t="n">
-        <v>831</v>
+      <c r="C293" s="5" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
@@ -18376,8 +18963,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C294" s="2" t="n">
-        <v>831</v>
+      <c r="C294" s="5" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
@@ -18437,8 +19026,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C295" s="2" t="n">
-        <v>300502</v>
+      <c r="C295" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
@@ -18498,8 +19089,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C296" s="2" t="n">
-        <v>2384</v>
+      <c r="C296" s="5" t="inlineStr">
+        <is>
+          <t>002384</t>
+        </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
@@ -18559,8 +19152,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C297" s="2" t="n">
-        <v>300516</v>
+      <c r="C297" s="5" t="inlineStr">
+        <is>
+          <t>300516</t>
+        </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
@@ -18620,8 +19215,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C298" s="2" t="n">
-        <v>300308</v>
+      <c r="C298" s="5" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
@@ -18681,8 +19278,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C299" s="2" t="n">
-        <v>688041</v>
+      <c r="C299" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
@@ -18742,8 +19341,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C300" s="2" t="n">
-        <v>2436</v>
+      <c r="C300" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
@@ -18803,8 +19404,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C301" s="2" t="n">
-        <v>300548</v>
+      <c r="C301" s="5" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
@@ -18864,8 +19467,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C302" s="2" t="n">
-        <v>300548</v>
+      <c r="C302" s="5" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
@@ -18925,8 +19530,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C303" s="2" t="n">
-        <v>2222</v>
+      <c r="C303" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
@@ -18986,8 +19593,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C304" s="2" t="n">
-        <v>2222</v>
+      <c r="C304" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
@@ -19047,8 +19656,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C305" s="2" t="n">
-        <v>300054</v>
+      <c r="C305" s="5" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
@@ -19108,8 +19719,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C306" s="2" t="n">
-        <v>688008</v>
+      <c r="C306" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
@@ -19169,8 +19782,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C307" s="2" t="n">
-        <v>688008</v>
+      <c r="C307" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
@@ -19230,8 +19845,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C308" s="2" t="n">
-        <v>601208</v>
+      <c r="C308" s="5" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
@@ -19291,8 +19908,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C309" s="2" t="n">
-        <v>600259</v>
+      <c r="C309" s="5" t="inlineStr">
+        <is>
+          <t>600259</t>
+        </is>
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
@@ -19352,8 +19971,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C310" s="2" t="n">
-        <v>600259</v>
+      <c r="C310" s="5" t="inlineStr">
+        <is>
+          <t>600259</t>
+        </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
@@ -19413,8 +20034,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C311" s="2" t="n">
-        <v>688778</v>
+      <c r="C311" s="5" t="inlineStr">
+        <is>
+          <t>688778</t>
+        </is>
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
@@ -19474,8 +20097,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C312" s="2" t="n">
-        <v>21</v>
+      <c r="C312" s="5" t="inlineStr">
+        <is>
+          <t>000021</t>
+        </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
@@ -19535,8 +20160,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C313" s="2" t="n">
-        <v>21</v>
+      <c r="C313" s="5" t="inlineStr">
+        <is>
+          <t>000021</t>
+        </is>
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
@@ -19596,8 +20223,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C314" s="2" t="n">
-        <v>831</v>
+      <c r="C314" s="5" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
@@ -19657,8 +20286,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C315" s="2" t="n">
-        <v>600498</v>
+      <c r="C315" s="5" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
@@ -19718,8 +20349,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C316" s="2" t="n">
-        <v>600259</v>
+      <c r="C316" s="5" t="inlineStr">
+        <is>
+          <t>600259</t>
+        </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
@@ -19779,8 +20412,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C317" s="2" t="n">
-        <v>300548</v>
+      <c r="C317" s="5" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
@@ -19840,8 +20475,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C318" s="2" t="n">
-        <v>300548</v>
+      <c r="C318" s="5" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
@@ -19901,8 +20538,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C319" s="2" t="n">
-        <v>831</v>
+      <c r="C319" s="5" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
@@ -19962,8 +20601,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C320" s="2" t="n">
-        <v>2384</v>
+      <c r="C320" s="5" t="inlineStr">
+        <is>
+          <t>002384</t>
+        </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
@@ -20023,8 +20664,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C321" s="2" t="n">
-        <v>21</v>
+      <c r="C321" s="5" t="inlineStr">
+        <is>
+          <t>000021</t>
+        </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
@@ -20084,8 +20727,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C322" s="2" t="n">
-        <v>300502</v>
+      <c r="C322" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
@@ -20145,8 +20790,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C323" s="2" t="n">
-        <v>688008</v>
+      <c r="C323" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
@@ -20206,8 +20853,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C324" s="2" t="n">
-        <v>688008</v>
+      <c r="C324" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
@@ -20267,8 +20916,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C325" s="2" t="n">
-        <v>300394</v>
+      <c r="C325" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
@@ -20328,8 +20979,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C326" s="2" t="n">
-        <v>300394</v>
+      <c r="C326" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
@@ -20389,8 +21042,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C327" s="2" t="n">
-        <v>688041</v>
+      <c r="C327" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
@@ -20450,8 +21105,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C328" s="2" t="n">
-        <v>300308</v>
+      <c r="C328" s="5" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
@@ -20511,8 +21168,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C329" s="2" t="n">
-        <v>300394</v>
+      <c r="C329" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
@@ -20572,8 +21231,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C330" s="2" t="n">
-        <v>600498</v>
+      <c r="C330" s="5" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
@@ -20633,8 +21294,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C331" s="2" t="n">
-        <v>2436</v>
+      <c r="C331" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
@@ -20694,8 +21357,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C332" s="2" t="n">
-        <v>300548</v>
+      <c r="C332" s="5" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
@@ -20755,8 +21420,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C333" s="2" t="n">
-        <v>300502</v>
+      <c r="C333" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
@@ -20816,8 +21483,10 @@
           <t>平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C334" s="2" t="n">
-        <v>21</v>
+      <c r="C334" s="5" t="inlineStr">
+        <is>
+          <t>000021</t>
+        </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
@@ -20877,8 +21546,10 @@
           <t>平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C335" s="2" t="n">
-        <v>600498</v>
+      <c r="C335" s="5" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
@@ -20938,8 +21609,10 @@
           <t>平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C336" s="2" t="n">
-        <v>300548</v>
+      <c r="C336" s="5" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
@@ -20999,8 +21672,10 @@
           <t>平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C337" s="2" t="n">
-        <v>300548</v>
+      <c r="C337" s="5" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
@@ -21060,8 +21735,10 @@
           <t>平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C338" s="2" t="n">
-        <v>300516</v>
+      <c r="C338" s="5" t="inlineStr">
+        <is>
+          <t>300516</t>
+        </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
@@ -21121,8 +21798,10 @@
           <t>平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C339" s="2" t="n">
-        <v>601208</v>
+      <c r="C339" s="5" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
@@ -21182,8 +21861,10 @@
           <t>平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C340" s="2" t="n">
-        <v>300394</v>
+      <c r="C340" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
@@ -21243,8 +21924,10 @@
           <t>平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C341" s="2" t="n">
-        <v>300308</v>
+      <c r="C341" s="5" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
@@ -21304,8 +21987,10 @@
           <t>平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C342" s="2" t="n">
-        <v>2436</v>
+      <c r="C342" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
@@ -21365,8 +22050,10 @@
           <t>平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C343" s="2" t="n">
-        <v>2156</v>
+      <c r="C343" s="5" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
@@ -21426,8 +22113,10 @@
           <t>平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C344" s="2" t="n">
-        <v>2156</v>
+      <c r="C344" s="5" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
@@ -21487,8 +22176,10 @@
           <t>平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C345" s="2" t="n">
-        <v>300502</v>
+      <c r="C345" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
@@ -21548,8 +22239,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C346" s="2" t="n">
-        <v>2384</v>
+      <c r="C346" s="5" t="inlineStr">
+        <is>
+          <t>002384</t>
+        </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
@@ -21609,8 +22302,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C347" s="2" t="n">
-        <v>2384</v>
+      <c r="C347" s="5" t="inlineStr">
+        <is>
+          <t>002384</t>
+        </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
@@ -21670,8 +22365,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C348" s="2" t="n">
-        <v>300750</v>
+      <c r="C348" s="5" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
@@ -21731,8 +22428,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C349" s="2" t="n">
-        <v>300054</v>
+      <c r="C349" s="5" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
@@ -21792,8 +22491,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C350" s="2" t="n">
-        <v>21</v>
+      <c r="C350" s="5" t="inlineStr">
+        <is>
+          <t>000021</t>
+        </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
@@ -21853,8 +22554,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C351" s="2" t="n">
-        <v>688041</v>
+      <c r="C351" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
@@ -21914,8 +22617,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C352" s="2" t="n">
-        <v>300502</v>
+      <c r="C352" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
@@ -21975,8 +22680,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C353" s="2" t="n">
-        <v>300502</v>
+      <c r="C353" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
@@ -22036,8 +22743,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C354" s="2" t="n">
-        <v>300548</v>
+      <c r="C354" s="5" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
@@ -22097,8 +22806,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C355" s="2" t="n">
-        <v>2922</v>
+      <c r="C355" s="5" t="inlineStr">
+        <is>
+          <t>002922</t>
+        </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
@@ -22158,8 +22869,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C356" s="2" t="n">
-        <v>600259</v>
+      <c r="C356" s="5" t="inlineStr">
+        <is>
+          <t>600259</t>
+        </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
@@ -22219,8 +22932,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C357" s="2" t="n">
-        <v>688008</v>
+      <c r="C357" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
@@ -22280,8 +22995,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C358" s="2" t="n">
-        <v>688062</v>
+      <c r="C358" s="5" t="inlineStr">
+        <is>
+          <t>688062</t>
+        </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
@@ -22341,8 +23058,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C359" s="2" t="n">
-        <v>2436</v>
+      <c r="C359" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
@@ -22402,8 +23121,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C360" s="2" t="n">
-        <v>300308</v>
+      <c r="C360" s="5" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
@@ -22463,8 +23184,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C361" s="2" t="n">
-        <v>600498</v>
+      <c r="C361" s="5" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
@@ -22524,8 +23247,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C362" s="2" t="n">
-        <v>300502</v>
+      <c r="C362" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
@@ -22585,8 +23310,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C363" s="2" t="n">
-        <v>300394</v>
+      <c r="C363" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
@@ -22646,8 +23373,10 @@
           <t>手机账户</t>
         </is>
       </c>
-      <c r="C364" s="2" t="n">
-        <v>300308</v>
+      <c r="C364" s="5" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
@@ -22707,8 +23436,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C365" s="2" t="n">
-        <v>300660</v>
+      <c r="C365" s="5" t="inlineStr">
+        <is>
+          <t>300660</t>
+        </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
@@ -22768,8 +23499,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C366" s="2" t="n">
-        <v>300750</v>
+      <c r="C366" s="5" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
@@ -22829,8 +23562,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C367" s="2" t="n">
-        <v>21</v>
+      <c r="C367" s="5" t="inlineStr">
+        <is>
+          <t>000021</t>
+        </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
@@ -22890,8 +23625,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C368" s="2" t="n">
-        <v>688008</v>
+      <c r="C368" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
@@ -22951,8 +23688,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C369" s="2" t="n">
-        <v>688008</v>
+      <c r="C369" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
@@ -23012,8 +23751,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C370" s="2" t="n">
-        <v>300054</v>
+      <c r="C370" s="5" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
@@ -23073,8 +23814,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C371" s="2" t="n">
-        <v>603920</v>
+      <c r="C371" s="5" t="inlineStr">
+        <is>
+          <t>603920</t>
+        </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
@@ -23134,8 +23877,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C372" s="2" t="n">
-        <v>688041</v>
+      <c r="C372" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
@@ -23195,8 +23940,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C373" s="2" t="n">
-        <v>688041</v>
+      <c r="C373" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
@@ -23256,8 +24003,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C374" s="2" t="n">
-        <v>688008</v>
+      <c r="C374" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
@@ -23317,8 +24066,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C375" s="2" t="n">
-        <v>601208</v>
+      <c r="C375" s="5" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
@@ -23378,8 +24129,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C376" s="2" t="n">
-        <v>600498</v>
+      <c r="C376" s="5" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
@@ -23439,8 +24192,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C377" s="2" t="n">
-        <v>300548</v>
+      <c r="C377" s="5" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
@@ -23500,8 +24255,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C378" s="2" t="n">
-        <v>300502</v>
+      <c r="C378" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
@@ -23561,8 +24318,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C379" s="2" t="n">
-        <v>300274</v>
+      <c r="C379" s="5" t="inlineStr">
+        <is>
+          <t>300274</t>
+        </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
@@ -23622,8 +24381,10 @@
           <t>跨账户(平安账户+手机账户)</t>
         </is>
       </c>
-      <c r="C380" s="2" t="n">
-        <v>988</v>
+      <c r="C380" s="5" t="inlineStr">
+        <is>
+          <t>000988</t>
+        </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
@@ -23683,8 +24444,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C381" s="2" t="n">
-        <v>688008</v>
+      <c r="C381" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
@@ -23744,8 +24507,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C382" s="2" t="n">
-        <v>300308</v>
+      <c r="C382" s="5" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
@@ -23805,8 +24570,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C383" s="2" t="n">
-        <v>688041</v>
+      <c r="C383" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
@@ -23866,8 +24633,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C384" s="2" t="n">
-        <v>688041</v>
+      <c r="C384" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
@@ -23927,8 +24696,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C385" s="2" t="n">
-        <v>300502</v>
+      <c r="C385" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
@@ -23988,8 +24759,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C386" s="2" t="n">
-        <v>688008</v>
+      <c r="C386" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
@@ -24049,8 +24822,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C387" s="2" t="n">
-        <v>688008</v>
+      <c r="C387" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
@@ -24110,8 +24885,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C388" s="2" t="n">
-        <v>688041</v>
+      <c r="C388" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
@@ -24171,8 +24948,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C389" s="2" t="n">
-        <v>688041</v>
+      <c r="C389" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
@@ -24232,8 +25011,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C390" s="2" t="n">
-        <v>300502</v>
+      <c r="C390" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
@@ -24293,8 +25074,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C391" s="2" t="n">
-        <v>688041</v>
+      <c r="C391" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
@@ -24354,8 +25137,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C392" s="2" t="n">
-        <v>688041</v>
+      <c r="C392" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
@@ -24415,8 +25200,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C393" s="2" t="n">
-        <v>688008</v>
+      <c r="C393" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
@@ -24476,8 +25263,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C394" s="2" t="n">
-        <v>688008</v>
+      <c r="C394" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
@@ -24537,8 +25326,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C395" s="2" t="n">
-        <v>300502</v>
+      <c r="C395" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
@@ -24598,8 +25389,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C396" s="2" t="n">
-        <v>688008</v>
+      <c r="C396" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
@@ -24659,8 +25452,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C397" s="2" t="n">
-        <v>688041</v>
+      <c r="C397" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
@@ -24720,8 +25515,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C398" s="2" t="n">
-        <v>688008</v>
+      <c r="C398" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
@@ -24781,8 +25578,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C399" s="2" t="n">
-        <v>688041</v>
+      <c r="C399" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
@@ -24842,8 +25641,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C400" s="2" t="n">
-        <v>688041</v>
+      <c r="C400" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
@@ -24903,8 +25704,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C401" s="2" t="n">
-        <v>300394</v>
+      <c r="C401" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
@@ -24964,8 +25767,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C402" s="2" t="n">
-        <v>688041</v>
+      <c r="C402" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
@@ -25025,8 +25830,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C403" s="2" t="n">
-        <v>688041</v>
+      <c r="C403" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
@@ -25086,8 +25893,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C404" s="2" t="n">
-        <v>300750</v>
+      <c r="C404" s="5" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
@@ -25147,8 +25956,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C405" s="2" t="n">
-        <v>688008</v>
+      <c r="C405" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
@@ -25208,8 +26019,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C406" s="2" t="n">
-        <v>688008</v>
+      <c r="C406" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
@@ -25269,8 +26082,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C407" s="2" t="n">
-        <v>300054</v>
+      <c r="C407" s="5" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
@@ -25330,8 +26145,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C408" s="2" t="n">
-        <v>2594</v>
+      <c r="C408" s="5" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
@@ -25391,8 +26208,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C409" s="2" t="n">
-        <v>688008</v>
+      <c r="C409" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
@@ -25452,8 +26271,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C410" s="2" t="n">
-        <v>300750</v>
+      <c r="C410" s="5" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
@@ -25513,8 +26334,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C411" s="2" t="n">
-        <v>688041</v>
+      <c r="C411" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
@@ -25574,8 +26397,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C412" s="2" t="n">
-        <v>688008</v>
+      <c r="C412" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
@@ -25635,8 +26460,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C413" s="2" t="n">
-        <v>688008</v>
+      <c r="C413" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
@@ -25696,8 +26523,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C414" s="2" t="n">
-        <v>2384</v>
+      <c r="C414" s="5" t="inlineStr">
+        <is>
+          <t>002384</t>
+        </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
@@ -25757,8 +26586,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C415" s="2" t="n">
-        <v>688041</v>
+      <c r="C415" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
@@ -25818,8 +26649,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C416" s="2" t="n">
-        <v>300308</v>
+      <c r="C416" s="5" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
@@ -25879,8 +26712,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C417" s="2" t="n">
-        <v>300308</v>
+      <c r="C417" s="5" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
@@ -25940,8 +26775,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C418" s="2" t="n">
-        <v>2156</v>
+      <c r="C418" s="5" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
@@ -26001,8 +26838,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C419" s="2" t="n">
-        <v>2156</v>
+      <c r="C419" s="5" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
@@ -26062,8 +26901,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C420" s="2" t="n">
-        <v>300750</v>
+      <c r="C420" s="5" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
@@ -26123,8 +26964,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C421" s="2" t="n">
-        <v>300548</v>
+      <c r="C421" s="5" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
@@ -26184,8 +27027,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C422" s="2" t="n">
-        <v>300394</v>
+      <c r="C422" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
@@ -26245,8 +27090,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C423" s="2" t="n">
-        <v>300502</v>
+      <c r="C423" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
@@ -26306,8 +27153,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C424" s="2" t="n">
-        <v>601208</v>
+      <c r="C424" s="5" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
@@ -26367,8 +27216,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C425" s="2" t="n">
-        <v>2384</v>
+      <c r="C425" s="5" t="inlineStr">
+        <is>
+          <t>002384</t>
+        </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
@@ -26428,8 +27279,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C426" s="2" t="n">
-        <v>2222</v>
+      <c r="C426" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
@@ -26489,8 +27342,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C427" s="2" t="n">
-        <v>688041</v>
+      <c r="C427" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
@@ -26550,8 +27405,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C428" s="2" t="n">
-        <v>2156</v>
+      <c r="C428" s="5" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
@@ -26611,8 +27468,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C429" s="2" t="n">
-        <v>2156</v>
+      <c r="C429" s="5" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
@@ -26672,8 +27531,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C430" s="2" t="n">
-        <v>21</v>
+      <c r="C430" s="5" t="inlineStr">
+        <is>
+          <t>000021</t>
+        </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
@@ -26733,8 +27594,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C431" s="2" t="n">
-        <v>688008</v>
+      <c r="C431" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
@@ -26794,8 +27657,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C432" s="2" t="n">
-        <v>688041</v>
+      <c r="C432" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
@@ -26855,8 +27720,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C433" s="2" t="n">
-        <v>300750</v>
+      <c r="C433" s="5" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
@@ -26916,8 +27783,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C434" s="2" t="n">
-        <v>300750</v>
+      <c r="C434" s="5" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
@@ -26977,8 +27846,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C435" s="2" t="n">
-        <v>688008</v>
+      <c r="C435" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
@@ -27038,8 +27909,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C436" s="2" t="n">
-        <v>688041</v>
+      <c r="C436" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
@@ -27099,8 +27972,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C437" s="2" t="n">
-        <v>688041</v>
+      <c r="C437" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
@@ -27160,8 +28035,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C438" s="2" t="n">
-        <v>300548</v>
+      <c r="C438" s="5" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
@@ -27221,8 +28098,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C439" s="2" t="n">
-        <v>688008</v>
+      <c r="C439" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
@@ -27282,8 +28161,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C440" s="2" t="n">
-        <v>300394</v>
+      <c r="C440" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
@@ -27343,8 +28224,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C441" s="2" t="n">
-        <v>688041</v>
+      <c r="C441" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
@@ -27404,8 +28287,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C442" s="2" t="n">
-        <v>688041</v>
+      <c r="C442" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
@@ -27465,8 +28350,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C443" s="2" t="n">
-        <v>300502</v>
+      <c r="C443" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
@@ -27526,8 +28413,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C444" s="2" t="n">
-        <v>300502</v>
+      <c r="C444" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
@@ -27587,8 +28476,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C445" s="2" t="n">
-        <v>688041</v>
+      <c r="C445" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
@@ -27648,8 +28539,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C446" s="2" t="n">
-        <v>688041</v>
+      <c r="C446" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
@@ -27709,8 +28602,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C447" s="2" t="n">
-        <v>300502</v>
+      <c r="C447" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
@@ -27770,8 +28665,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C448" s="2" t="n">
-        <v>688008</v>
+      <c r="C448" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
@@ -27831,8 +28728,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C449" s="2" t="n">
-        <v>300502</v>
+      <c r="C449" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
@@ -27892,8 +28791,10 @@
           <t>平安账户</t>
         </is>
       </c>
-      <c r="C450" s="2" t="n">
-        <v>688676</v>
+      <c r="C450" s="5" t="inlineStr">
+        <is>
+          <t>688676</t>
+        </is>
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
@@ -27953,8 +28854,10 @@
           <t>平安账户</t>
         </is>
       </c>
-      <c r="C451" s="2" t="n">
-        <v>603920</v>
+      <c r="C451" s="5" t="inlineStr">
+        <is>
+          <t>603920</t>
+        </is>
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
@@ -28014,8 +28917,10 @@
           <t>平安账户</t>
         </is>
       </c>
-      <c r="C452" s="2" t="n">
-        <v>2222</v>
+      <c r="C452" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
@@ -28075,8 +28980,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C453" s="2" t="n">
-        <v>300502</v>
+      <c r="C453" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
@@ -28136,8 +29043,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C454" s="2" t="n">
-        <v>688041</v>
+      <c r="C454" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
@@ -28197,8 +29106,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C455" s="2" t="n">
-        <v>688041</v>
+      <c r="C455" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
@@ -28258,8 +29169,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C456" s="2" t="n">
-        <v>300548</v>
+      <c r="C456" s="5" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
@@ -28319,8 +29232,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C457" s="2" t="n">
-        <v>300502</v>
+      <c r="C457" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
@@ -28380,8 +29295,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C458" s="2" t="n">
-        <v>688041</v>
+      <c r="C458" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
@@ -28441,8 +29358,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C459" s="2" t="n">
-        <v>300308</v>
+      <c r="C459" s="5" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
@@ -28502,8 +29421,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C460" s="2" t="n">
-        <v>2594</v>
+      <c r="C460" s="5" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
@@ -28563,8 +29484,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C461" s="2" t="n">
-        <v>300394</v>
+      <c r="C461" s="5" t="inlineStr">
+        <is>
+          <t>300394</t>
+        </is>
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
@@ -28624,8 +29547,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C462" s="2" t="n">
-        <v>300502</v>
+      <c r="C462" s="5" t="inlineStr">
+        <is>
+          <t>300502</t>
+        </is>
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
@@ -28685,8 +29610,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C463" s="2" t="n">
-        <v>688041</v>
+      <c r="C463" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
@@ -28746,8 +29673,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C464" s="2" t="n">
-        <v>300548</v>
+      <c r="C464" s="5" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
@@ -28807,8 +29736,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C465" s="2" t="n">
-        <v>300054</v>
+      <c r="C465" s="5" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
@@ -28868,8 +29799,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C466" s="2" t="n">
-        <v>2384</v>
+      <c r="C466" s="5" t="inlineStr">
+        <is>
+          <t>002384</t>
+        </is>
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
@@ -28929,8 +29862,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C467" s="2" t="n">
-        <v>688008</v>
+      <c r="C467" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
@@ -28990,8 +29925,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C468" s="2" t="n">
-        <v>300308</v>
+      <c r="C468" s="5" t="inlineStr">
+        <is>
+          <t>300308</t>
+        </is>
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
@@ -29051,8 +29988,10 @@
           <t>跨账户(两融账户+手机账户)</t>
         </is>
       </c>
-      <c r="C469" s="2" t="n">
-        <v>2594</v>
+      <c r="C469" s="5" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
@@ -29112,8 +30051,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C470" s="2" t="n">
-        <v>688041</v>
+      <c r="C470" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
@@ -29173,8 +30114,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C471" s="2" t="n">
-        <v>688008</v>
+      <c r="C471" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
@@ -29234,8 +30177,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C472" s="2" t="n">
-        <v>688008</v>
+      <c r="C472" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
@@ -29295,8 +30240,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C473" s="2" t="n">
-        <v>688008</v>
+      <c r="C473" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
@@ -29356,8 +30303,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C474" s="2" t="n">
-        <v>688008</v>
+      <c r="C474" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
@@ -29417,8 +30366,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C475" s="2" t="n">
-        <v>300750</v>
+      <c r="C475" s="5" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
@@ -29478,8 +30429,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C476" s="2" t="n">
-        <v>688041</v>
+      <c r="C476" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
@@ -29539,8 +30492,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C477" s="2" t="n">
-        <v>988</v>
+      <c r="C477" s="5" t="inlineStr">
+        <is>
+          <t>000988</t>
+        </is>
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
@@ -29600,8 +30555,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C478" s="2" t="n">
-        <v>688778</v>
+      <c r="C478" s="5" t="inlineStr">
+        <is>
+          <t>688778</t>
+        </is>
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
@@ -29661,8 +30618,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C479" s="2" t="n">
-        <v>2156</v>
+      <c r="C479" s="5" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
@@ -29722,8 +30681,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C480" s="2" t="n">
-        <v>561980</v>
+      <c r="C480" s="5" t="inlineStr">
+        <is>
+          <t>561980</t>
+        </is>
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
@@ -29783,8 +30744,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C481" s="2" t="n">
-        <v>600259</v>
+      <c r="C481" s="5" t="inlineStr">
+        <is>
+          <t>600259</t>
+        </is>
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
@@ -29844,8 +30807,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C482" s="2" t="n">
-        <v>512760</v>
+      <c r="C482" s="5" t="inlineStr">
+        <is>
+          <t>512760</t>
+        </is>
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
@@ -29905,8 +30870,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C483" s="2" t="n">
-        <v>688041</v>
+      <c r="C483" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
@@ -29966,8 +30933,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C484" s="2" t="n">
-        <v>688041</v>
+      <c r="C484" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
@@ -30027,8 +30996,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C485" s="2" t="n">
-        <v>300054</v>
+      <c r="C485" s="5" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
@@ -30088,8 +31059,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C486" s="2" t="n">
-        <v>688008</v>
+      <c r="C486" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
@@ -30149,8 +31122,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C487" s="2" t="n">
-        <v>561980</v>
+      <c r="C487" s="5" t="inlineStr">
+        <is>
+          <t>561980</t>
+        </is>
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
@@ -30210,8 +31185,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C488" s="2" t="n">
-        <v>2436</v>
+      <c r="C488" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
@@ -30271,8 +31248,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C489" s="2" t="n">
-        <v>512760</v>
+      <c r="C489" s="5" t="inlineStr">
+        <is>
+          <t>512760</t>
+        </is>
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
@@ -30332,8 +31311,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C490" s="2" t="n">
-        <v>831</v>
+      <c r="C490" s="5" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
@@ -30393,8 +31374,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C491" s="2" t="n">
-        <v>831</v>
+      <c r="C491" s="5" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
@@ -30454,8 +31437,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C492" s="2" t="n">
-        <v>688008</v>
+      <c r="C492" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
@@ -30515,8 +31500,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C493" s="2" t="n">
-        <v>688041</v>
+      <c r="C493" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
@@ -30576,8 +31563,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C494" s="2" t="n">
-        <v>688041</v>
+      <c r="C494" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
@@ -30637,8 +31626,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C495" s="2" t="n">
-        <v>600259</v>
+      <c r="C495" s="5" t="inlineStr">
+        <is>
+          <t>600259</t>
+        </is>
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
@@ -30698,8 +31689,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C496" s="2" t="n">
-        <v>300054</v>
+      <c r="C496" s="5" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
@@ -30759,8 +31752,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C497" s="2" t="n">
-        <v>601208</v>
+      <c r="C497" s="5" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
@@ -30820,8 +31815,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C498" s="2" t="n">
-        <v>561980</v>
+      <c r="C498" s="5" t="inlineStr">
+        <is>
+          <t>561980</t>
+        </is>
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
@@ -30881,8 +31878,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C499" s="2" t="n">
-        <v>561980</v>
+      <c r="C499" s="5" t="inlineStr">
+        <is>
+          <t>561980</t>
+        </is>
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
@@ -30942,8 +31941,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C500" s="2" t="n">
-        <v>688008</v>
+      <c r="C500" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
@@ -31003,8 +32004,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C501" s="2" t="n">
-        <v>688008</v>
+      <c r="C501" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
@@ -31064,8 +32067,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C502" s="2" t="n">
-        <v>688041</v>
+      <c r="C502" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
@@ -31125,8 +32130,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C503" s="2" t="n">
-        <v>688008</v>
+      <c r="C503" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
@@ -31186,8 +32193,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C504" s="2" t="n">
-        <v>512760</v>
+      <c r="C504" s="5" t="inlineStr">
+        <is>
+          <t>512760</t>
+        </is>
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
@@ -31247,8 +32256,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C505" s="2" t="n">
-        <v>561980</v>
+      <c r="C505" s="5" t="inlineStr">
+        <is>
+          <t>561980</t>
+        </is>
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
@@ -31308,8 +32319,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C506" s="2" t="n">
-        <v>988</v>
+      <c r="C506" s="5" t="inlineStr">
+        <is>
+          <t>000988</t>
+        </is>
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
@@ -31369,8 +32382,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C507" s="2" t="n">
-        <v>300054</v>
+      <c r="C507" s="5" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
@@ -31430,8 +32445,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C508" s="2" t="n">
-        <v>601208</v>
+      <c r="C508" s="5" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
@@ -31491,8 +32508,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C509" s="2" t="n">
-        <v>512760</v>
+      <c r="C509" s="5" t="inlineStr">
+        <is>
+          <t>512760</t>
+        </is>
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
@@ -31552,8 +32571,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C510" s="2" t="n">
-        <v>688041</v>
+      <c r="C510" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
@@ -31613,8 +32634,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C511" s="2" t="n">
-        <v>600259</v>
+      <c r="C511" s="5" t="inlineStr">
+        <is>
+          <t>600259</t>
+        </is>
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
@@ -31674,8 +32697,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C512" s="2" t="n">
-        <v>2156</v>
+      <c r="C512" s="5" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
@@ -31735,8 +32760,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C513" s="2" t="n">
-        <v>2222</v>
+      <c r="C513" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
@@ -31796,8 +32823,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C514" s="2" t="n">
-        <v>988</v>
+      <c r="C514" s="5" t="inlineStr">
+        <is>
+          <t>000988</t>
+        </is>
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
@@ -31857,8 +32886,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C515" s="2" t="n">
-        <v>831</v>
+      <c r="C515" s="5" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
@@ -31918,8 +32949,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C516" s="2" t="n">
-        <v>831</v>
+      <c r="C516" s="5" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
@@ -31979,8 +33012,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C517" s="2" t="n">
-        <v>561980</v>
+      <c r="C517" s="5" t="inlineStr">
+        <is>
+          <t>561980</t>
+        </is>
       </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
@@ -32040,8 +33075,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C518" s="2" t="n">
-        <v>600498</v>
+      <c r="C518" s="5" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
@@ -32101,8 +33138,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C519" s="2" t="n">
-        <v>512760</v>
+      <c r="C519" s="5" t="inlineStr">
+        <is>
+          <t>512760</t>
+        </is>
       </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
@@ -32162,8 +33201,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C520" s="2" t="n">
-        <v>2594</v>
+      <c r="C520" s="5" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
@@ -32223,8 +33264,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C521" s="2" t="n">
-        <v>688008</v>
+      <c r="C521" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
@@ -32284,8 +33327,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C522" s="2" t="n">
-        <v>300548</v>
+      <c r="C522" s="5" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
       </c>
       <c r="D522" s="2" t="inlineStr">
         <is>
@@ -32345,8 +33390,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C523" s="2" t="n">
-        <v>561980</v>
+      <c r="C523" s="5" t="inlineStr">
+        <is>
+          <t>561980</t>
+        </is>
       </c>
       <c r="D523" s="2" t="inlineStr">
         <is>
@@ -32406,8 +33453,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C524" s="2" t="n">
-        <v>2222</v>
+      <c r="C524" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
@@ -32467,8 +33516,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C525" s="2" t="n">
-        <v>561980</v>
+      <c r="C525" s="5" t="inlineStr">
+        <is>
+          <t>561980</t>
+        </is>
       </c>
       <c r="D525" s="2" t="inlineStr">
         <is>
@@ -32528,8 +33579,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C526" s="2" t="n">
-        <v>600498</v>
+      <c r="C526" s="5" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
@@ -32589,8 +33642,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C527" s="2" t="n">
-        <v>2594</v>
+      <c r="C527" s="5" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
       </c>
       <c r="D527" s="2" t="inlineStr">
         <is>
@@ -32650,8 +33705,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C528" s="2" t="n">
-        <v>2436</v>
+      <c r="C528" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D528" s="2" t="inlineStr">
         <is>
@@ -32711,8 +33768,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C529" s="2" t="n">
-        <v>300548</v>
+      <c r="C529" s="5" t="inlineStr">
+        <is>
+          <t>300548</t>
+        </is>
       </c>
       <c r="D529" s="2" t="inlineStr">
         <is>
@@ -32772,8 +33831,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C530" s="2" t="n">
-        <v>300750</v>
+      <c r="C530" s="5" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
       </c>
       <c r="D530" s="2" t="inlineStr">
         <is>
@@ -32833,8 +33894,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C531" s="2" t="n">
-        <v>512760</v>
+      <c r="C531" s="5" t="inlineStr">
+        <is>
+          <t>512760</t>
+        </is>
       </c>
       <c r="D531" s="2" t="inlineStr">
         <is>
@@ -32894,8 +33957,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C532" s="2" t="n">
-        <v>688008</v>
+      <c r="C532" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D532" s="2" t="inlineStr">
         <is>
@@ -32955,8 +34020,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C533" s="2" t="n">
-        <v>561980</v>
+      <c r="C533" s="5" t="inlineStr">
+        <is>
+          <t>561980</t>
+        </is>
       </c>
       <c r="D533" s="2" t="inlineStr">
         <is>
@@ -33016,8 +34083,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C534" s="2" t="n">
-        <v>831</v>
+      <c r="C534" s="5" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
       </c>
       <c r="D534" s="2" t="inlineStr">
         <is>
@@ -33077,8 +34146,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C535" s="2" t="n">
-        <v>600498</v>
+      <c r="C535" s="5" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
       </c>
       <c r="D535" s="2" t="inlineStr">
         <is>
@@ -33138,8 +34209,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C536" s="2" t="n">
-        <v>688008</v>
+      <c r="C536" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D536" s="2" t="inlineStr">
         <is>
@@ -33199,8 +34272,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C537" s="2" t="n">
-        <v>688008</v>
+      <c r="C537" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D537" s="2" t="inlineStr">
         <is>
@@ -33260,8 +34335,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C538" s="2" t="n">
-        <v>512760</v>
+      <c r="C538" s="5" t="inlineStr">
+        <is>
+          <t>512760</t>
+        </is>
       </c>
       <c r="D538" s="2" t="inlineStr">
         <is>
@@ -33321,8 +34398,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C539" s="2" t="n">
-        <v>2436</v>
+      <c r="C539" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D539" s="2" t="inlineStr">
         <is>
@@ -33382,8 +34461,10 @@
           <t>跨账户(两融账户+手机账户)</t>
         </is>
       </c>
-      <c r="C540" s="2" t="n">
-        <v>2594</v>
+      <c r="C540" s="5" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
       </c>
       <c r="D540" s="2" t="inlineStr">
         <is>
@@ -33443,8 +34524,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C541" s="2" t="n">
-        <v>600498</v>
+      <c r="C541" s="5" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
       </c>
       <c r="D541" s="2" t="inlineStr">
         <is>
@@ -33504,8 +34587,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C542" s="2" t="n">
-        <v>831</v>
+      <c r="C542" s="5" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
       </c>
       <c r="D542" s="2" t="inlineStr">
         <is>
@@ -33565,8 +34650,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C543" s="2" t="n">
-        <v>512760</v>
+      <c r="C543" s="5" t="inlineStr">
+        <is>
+          <t>512760</t>
+        </is>
       </c>
       <c r="D543" s="2" t="inlineStr">
         <is>
@@ -33626,8 +34713,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C544" s="2" t="n">
-        <v>688041</v>
+      <c r="C544" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D544" s="2" t="inlineStr">
         <is>
@@ -33687,8 +34776,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C545" s="2" t="n">
-        <v>561980</v>
+      <c r="C545" s="5" t="inlineStr">
+        <is>
+          <t>561980</t>
+        </is>
       </c>
       <c r="D545" s="2" t="inlineStr">
         <is>
@@ -33748,8 +34839,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C546" s="2" t="n">
-        <v>688008</v>
+      <c r="C546" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D546" s="2" t="inlineStr">
         <is>
@@ -33809,8 +34902,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C547" s="2" t="n">
-        <v>2837</v>
+      <c r="C547" s="5" t="inlineStr">
+        <is>
+          <t>002837</t>
+        </is>
       </c>
       <c r="D547" s="2" t="inlineStr">
         <is>
@@ -33870,8 +34965,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C548" s="2" t="n">
-        <v>601208</v>
+      <c r="C548" s="5" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
       </c>
       <c r="D548" s="2" t="inlineStr">
         <is>
@@ -33931,8 +35028,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C549" s="2" t="n">
-        <v>2594</v>
+      <c r="C549" s="5" t="inlineStr">
+        <is>
+          <t>002594</t>
+        </is>
       </c>
       <c r="D549" s="2" t="inlineStr">
         <is>
@@ -33992,8 +35091,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C550" s="2" t="n">
-        <v>831</v>
+      <c r="C550" s="5" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
       </c>
       <c r="D550" s="2" t="inlineStr">
         <is>
@@ -34053,8 +35154,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C551" s="2" t="n">
-        <v>2156</v>
+      <c r="C551" s="5" t="inlineStr">
+        <is>
+          <t>002156</t>
+        </is>
       </c>
       <c r="D551" s="2" t="inlineStr">
         <is>
@@ -34114,8 +35217,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C552" s="2" t="n">
-        <v>601208</v>
+      <c r="C552" s="5" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
       </c>
       <c r="D552" s="2" t="inlineStr">
         <is>
@@ -34175,8 +35280,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C553" s="2" t="n">
-        <v>2837</v>
+      <c r="C553" s="5" t="inlineStr">
+        <is>
+          <t>002837</t>
+        </is>
       </c>
       <c r="D553" s="2" t="inlineStr">
         <is>
@@ -34236,8 +35343,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C554" s="2" t="n">
-        <v>688008</v>
+      <c r="C554" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D554" s="2" t="inlineStr">
         <is>
@@ -34297,8 +35406,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C555" s="2" t="n">
-        <v>2837</v>
+      <c r="C555" s="5" t="inlineStr">
+        <is>
+          <t>002837</t>
+        </is>
       </c>
       <c r="D555" s="2" t="inlineStr">
         <is>
@@ -34358,8 +35469,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C556" s="2" t="n">
-        <v>831</v>
+      <c r="C556" s="5" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
       </c>
       <c r="D556" s="2" t="inlineStr">
         <is>
@@ -34419,8 +35532,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C557" s="2" t="n">
-        <v>2436</v>
+      <c r="C557" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D557" s="2" t="inlineStr">
         <is>
@@ -34480,8 +35595,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C558" s="2" t="n">
-        <v>512760</v>
+      <c r="C558" s="5" t="inlineStr">
+        <is>
+          <t>512760</t>
+        </is>
       </c>
       <c r="D558" s="2" t="inlineStr">
         <is>
@@ -34541,8 +35658,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C559" s="2" t="n">
-        <v>561980</v>
+      <c r="C559" s="5" t="inlineStr">
+        <is>
+          <t>561980</t>
+        </is>
       </c>
       <c r="D559" s="2" t="inlineStr">
         <is>
@@ -34602,8 +35721,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C560" s="2" t="n">
-        <v>688778</v>
+      <c r="C560" s="5" t="inlineStr">
+        <is>
+          <t>688778</t>
+        </is>
       </c>
       <c r="D560" s="2" t="inlineStr">
         <is>
@@ -34663,8 +35784,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C561" s="2" t="n">
-        <v>688008</v>
+      <c r="C561" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D561" s="2" t="inlineStr">
         <is>
@@ -34724,8 +35847,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C562" s="2" t="n">
-        <v>831</v>
+      <c r="C562" s="5" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
       </c>
       <c r="D562" s="2" t="inlineStr">
         <is>
@@ -34785,8 +35910,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C563" s="2" t="n">
-        <v>2436</v>
+      <c r="C563" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D563" s="2" t="inlineStr">
         <is>
@@ -34846,8 +35973,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C564" s="2" t="n">
-        <v>2837</v>
+      <c r="C564" s="5" t="inlineStr">
+        <is>
+          <t>002837</t>
+        </is>
       </c>
       <c r="D564" s="2" t="inlineStr">
         <is>
@@ -34907,8 +36036,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C565" s="2" t="n">
-        <v>688008</v>
+      <c r="C565" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D565" s="2" t="inlineStr">
         <is>
@@ -34968,8 +36099,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C566" s="2" t="n">
-        <v>2222</v>
+      <c r="C566" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D566" s="2" t="inlineStr">
         <is>
@@ -35029,8 +36162,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C567" s="2" t="n">
-        <v>601208</v>
+      <c r="C567" s="5" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
       </c>
       <c r="D567" s="2" t="inlineStr">
         <is>
@@ -35090,8 +36225,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C568" s="2" t="n">
-        <v>688008</v>
+      <c r="C568" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D568" s="2" t="inlineStr">
         <is>
@@ -35151,8 +36288,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C569" s="2" t="n">
-        <v>2436</v>
+      <c r="C569" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D569" s="2" t="inlineStr">
         <is>
@@ -35212,8 +36351,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C570" s="2" t="n">
-        <v>2222</v>
+      <c r="C570" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D570" s="2" t="inlineStr">
         <is>
@@ -35273,8 +36414,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C571" s="2" t="n">
-        <v>2837</v>
+      <c r="C571" s="5" t="inlineStr">
+        <is>
+          <t>002837</t>
+        </is>
       </c>
       <c r="D571" s="2" t="inlineStr">
         <is>
@@ -35334,8 +36477,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C572" s="2" t="n">
-        <v>688041</v>
+      <c r="C572" s="5" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
       </c>
       <c r="D572" s="2" t="inlineStr">
         <is>
@@ -35395,8 +36540,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C573" s="2" t="n">
-        <v>601208</v>
+      <c r="C573" s="5" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
       </c>
       <c r="D573" s="2" t="inlineStr">
         <is>
@@ -35456,8 +36603,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C574" s="2" t="n">
-        <v>300054</v>
+      <c r="C574" s="5" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
       </c>
       <c r="D574" s="2" t="inlineStr">
         <is>
@@ -35517,8 +36666,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C575" s="2" t="n">
-        <v>2436</v>
+      <c r="C575" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D575" s="2" t="inlineStr">
         <is>
@@ -35578,8 +36729,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C576" s="2" t="n">
-        <v>2436</v>
+      <c r="C576" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D576" s="2" t="inlineStr">
         <is>
@@ -35639,8 +36792,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C577" s="2" t="n">
-        <v>2837</v>
+      <c r="C577" s="5" t="inlineStr">
+        <is>
+          <t>002837</t>
+        </is>
       </c>
       <c r="D577" s="2" t="inlineStr">
         <is>
@@ -35700,8 +36855,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C578" s="2" t="n">
-        <v>561980</v>
+      <c r="C578" s="5" t="inlineStr">
+        <is>
+          <t>561980</t>
+        </is>
       </c>
       <c r="D578" s="2" t="inlineStr">
         <is>
@@ -35761,8 +36918,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C579" s="2" t="n">
-        <v>688008</v>
+      <c r="C579" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D579" s="2" t="inlineStr">
         <is>
@@ -35822,8 +36981,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C580" s="2" t="n">
-        <v>688008</v>
+      <c r="C580" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D580" s="2" t="inlineStr">
         <is>
@@ -35883,8 +37044,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C581" s="2" t="n">
-        <v>831</v>
+      <c r="C581" s="5" t="inlineStr">
+        <is>
+          <t>000831</t>
+        </is>
       </c>
       <c r="D581" s="2" t="inlineStr">
         <is>
@@ -35944,8 +37107,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C582" s="2" t="n">
-        <v>2222</v>
+      <c r="C582" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D582" s="2" t="inlineStr">
         <is>
@@ -36005,8 +37170,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C583" s="2" t="n">
-        <v>688008</v>
+      <c r="C583" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D583" s="2" t="inlineStr">
         <is>
@@ -36066,8 +37233,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C584" s="2" t="n">
-        <v>2222</v>
+      <c r="C584" s="5" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
       </c>
       <c r="D584" s="2" t="inlineStr">
         <is>
@@ -36127,8 +37296,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C585" s="2" t="n">
-        <v>300054</v>
+      <c r="C585" s="5" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
       </c>
       <c r="D585" s="2" t="inlineStr">
         <is>
@@ -36188,8 +37359,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C586" s="2" t="n">
-        <v>988</v>
+      <c r="C586" s="5" t="inlineStr">
+        <is>
+          <t>000988</t>
+        </is>
       </c>
       <c r="D586" s="2" t="inlineStr">
         <is>
@@ -36249,8 +37422,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C587" s="2" t="n">
-        <v>2384</v>
+      <c r="C587" s="5" t="inlineStr">
+        <is>
+          <t>002384</t>
+        </is>
       </c>
       <c r="D587" s="2" t="inlineStr">
         <is>
@@ -36310,8 +37485,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C588" s="2" t="n">
-        <v>600498</v>
+      <c r="C588" s="5" t="inlineStr">
+        <is>
+          <t>600498</t>
+        </is>
       </c>
       <c r="D588" s="2" t="inlineStr">
         <is>
@@ -36371,8 +37548,10 @@
           <t>两融账户+平安账户+手机账户</t>
         </is>
       </c>
-      <c r="C589" s="2" t="n">
-        <v>2436</v>
+      <c r="C589" s="5" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
       </c>
       <c r="D589" s="2" t="inlineStr">
         <is>
@@ -36432,8 +37611,10 @@
           <t>跨账户(两融账户+手机账户)</t>
         </is>
       </c>
-      <c r="C590" s="2" t="n">
-        <v>300750</v>
+      <c r="C590" s="5" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
       </c>
       <c r="D590" s="2" t="inlineStr">
         <is>
@@ -36493,8 +37674,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C591" s="2" t="n">
-        <v>601208</v>
+      <c r="C591" s="5" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
       </c>
       <c r="D591" s="2" t="inlineStr">
         <is>
@@ -36554,8 +37737,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C592" s="2" t="n">
-        <v>300054</v>
+      <c r="C592" s="5" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
       </c>
       <c r="D592" s="2" t="inlineStr">
         <is>
@@ -36615,8 +37800,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C593" s="2" t="n">
-        <v>688008</v>
+      <c r="C593" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D593" s="2" t="inlineStr">
         <is>
@@ -36676,8 +37863,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C594" s="2" t="n">
-        <v>300054</v>
+      <c r="C594" s="5" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
       </c>
       <c r="D594" s="2" t="inlineStr">
         <is>
@@ -36737,8 +37926,10 @@
           <t>两融账户+平安账户</t>
         </is>
       </c>
-      <c r="C595" s="2" t="n">
-        <v>601208</v>
+      <c r="C595" s="5" t="inlineStr">
+        <is>
+          <t>601208</t>
+        </is>
       </c>
       <c r="D595" s="2" t="inlineStr">
         <is>
@@ -36798,8 +37989,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C596" s="2" t="n">
-        <v>300054</v>
+      <c r="C596" s="5" t="inlineStr">
+        <is>
+          <t>300054</t>
+        </is>
       </c>
       <c r="D596" s="2" t="inlineStr">
         <is>
@@ -36859,8 +38052,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C597" s="2" t="n">
-        <v>688008</v>
+      <c r="C597" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D597" s="2" t="inlineStr">
         <is>
@@ -36920,8 +38115,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C598" s="2" t="n">
-        <v>300750</v>
+      <c r="C598" s="5" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
       </c>
       <c r="D598" s="2" t="inlineStr">
         <is>
@@ -36981,8 +38178,10 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C599" s="2" t="n">
-        <v>603228</v>
+      <c r="C599" s="5" t="inlineStr">
+        <is>
+          <t>603228</t>
+        </is>
       </c>
       <c r="D599" s="2" t="inlineStr">
         <is>
@@ -37042,8 +38241,10 @@
           <t>两融账户</t>
         </is>
       </c>
-      <c r="C600" s="2" t="n">
-        <v>688008</v>
+      <c r="C600" s="5" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
       </c>
       <c r="D600" s="2" t="inlineStr">
         <is>
@@ -37103,7 +38304,7 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C601" s="2" t="inlineStr">
+      <c r="C601" s="5" t="inlineStr">
         <is>
           <t>002916</t>
         </is>
@@ -37166,7 +38367,7 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C602" s="2" t="inlineStr">
+      <c r="C602" s="5" t="inlineStr">
         <is>
           <t>688008</t>
         </is>
@@ -37229,7 +38430,7 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C603" s="2" t="inlineStr">
+      <c r="C603" s="5" t="inlineStr">
         <is>
           <t>002436</t>
         </is>
@@ -37292,7 +38493,7 @@
           <t>两融账户+手机账户</t>
         </is>
       </c>
-      <c r="C604" s="2" t="inlineStr">
+      <c r="C604" s="5" t="inlineStr">
         <is>
           <t>688041</t>
         </is>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q612"/>
+  <dimension ref="A1:Q624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -39049,6 +39049,762 @@
         </is>
       </c>
     </row>
+    <row r="613">
+      <c r="A613" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B613" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C613" s="3" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D613" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E613" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="F613" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="G613" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="H613" s="2" t="n">
+        <v>226.9702</v>
+      </c>
+      <c r="I613" s="2" t="n">
+        <v>229.6233</v>
+      </c>
+      <c r="J613" s="2" t="n">
+        <v>136182.11</v>
+      </c>
+      <c r="K613" s="2" t="n">
+        <v>137774</v>
+      </c>
+      <c r="L613" s="4" t="n">
+        <v>1591.89</v>
+      </c>
+      <c r="M613" s="2" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="N613" s="2" t="n">
+        <v>68.89</v>
+      </c>
+      <c r="O613" s="2" t="n">
+        <v>96.29000000000001</v>
+      </c>
+      <c r="P613" s="4" t="n">
+        <v>1495.6</v>
+      </c>
+      <c r="Q613" s="2" t="inlineStr">
+        <is>
+          <t>1.10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B614" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C614" s="3" t="inlineStr">
+        <is>
+          <t>603228</t>
+        </is>
+      </c>
+      <c r="D614" s="2" t="inlineStr">
+        <is>
+          <t>景旺电子</t>
+        </is>
+      </c>
+      <c r="E614" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F614" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G614" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H614" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="I614" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J614" s="2" t="n">
+        <v>10800</v>
+      </c>
+      <c r="K614" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L614" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M614" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N614" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O614" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P614" s="5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q614" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B615" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C615" s="3" t="inlineStr">
+        <is>
+          <t>688820</t>
+        </is>
+      </c>
+      <c r="D615" s="2" t="inlineStr">
+        <is>
+          <t>盛合晶微</t>
+        </is>
+      </c>
+      <c r="E615" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F615" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G615" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H615" s="2" t="n">
+        <v>139.2</v>
+      </c>
+      <c r="I615" s="2" t="n">
+        <v>140.74</v>
+      </c>
+      <c r="J615" s="2" t="n">
+        <v>27840</v>
+      </c>
+      <c r="K615" s="2" t="n">
+        <v>28148</v>
+      </c>
+      <c r="L615" s="4" t="n">
+        <v>308</v>
+      </c>
+      <c r="M615" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N615" s="2" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="O615" s="2" t="n">
+        <v>24.07</v>
+      </c>
+      <c r="P615" s="4" t="n">
+        <v>283.93</v>
+      </c>
+      <c r="Q615" s="2" t="inlineStr">
+        <is>
+          <t>1.02%</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B616" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C616" s="3" t="inlineStr">
+        <is>
+          <t>688820</t>
+        </is>
+      </c>
+      <c r="D616" s="2" t="inlineStr">
+        <is>
+          <t>盛合晶微</t>
+        </is>
+      </c>
+      <c r="E616" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F616" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G616" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H616" s="2" t="n">
+        <v>139.2</v>
+      </c>
+      <c r="I616" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J616" s="2" t="n">
+        <v>27840</v>
+      </c>
+      <c r="K616" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L616" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M616" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N616" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O616" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P616" s="5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q616" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B617" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C617" s="3" t="inlineStr">
+        <is>
+          <t>688603</t>
+        </is>
+      </c>
+      <c r="D617" s="2" t="inlineStr">
+        <is>
+          <t>天承科技</t>
+        </is>
+      </c>
+      <c r="E617" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="F617" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G617" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H617" s="2" t="n">
+        <v>122.39</v>
+      </c>
+      <c r="I617" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J617" s="2" t="n">
+        <v>19704.79</v>
+      </c>
+      <c r="K617" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L617" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M617" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N617" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O617" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P617" s="5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q617" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B618" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C618" s="3" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D618" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E618" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F618" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G618" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H618" s="2" t="n">
+        <v>45.195</v>
+      </c>
+      <c r="I618" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J618" s="2" t="n">
+        <v>9039</v>
+      </c>
+      <c r="K618" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L618" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M618" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N618" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O618" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P618" s="5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q618" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B619" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C619" s="3" t="inlineStr">
+        <is>
+          <t>600127</t>
+        </is>
+      </c>
+      <c r="D619" s="2" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="E619" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F619" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G619" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H619" s="2" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="I619" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J619" s="2" t="n">
+        <v>8015</v>
+      </c>
+      <c r="K619" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L619" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M619" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N619" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O619" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P619" s="5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q619" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B620" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C620" s="3" t="inlineStr">
+        <is>
+          <t>688062</t>
+        </is>
+      </c>
+      <c r="D620" s="2" t="inlineStr">
+        <is>
+          <t>迈威生物</t>
+        </is>
+      </c>
+      <c r="E620" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F620" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G620" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H620" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I620" s="2" t="n">
+        <v>27.77</v>
+      </c>
+      <c r="J620" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K620" s="2" t="n">
+        <v>13885</v>
+      </c>
+      <c r="L620" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M620" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N620" s="2" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="O620" s="2" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="P620" s="5" t="n">
+        <v>-11.94</v>
+      </c>
+      <c r="Q620" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B621" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C621" s="3" t="inlineStr">
+        <is>
+          <t>561980</t>
+        </is>
+      </c>
+      <c r="D621" s="2" t="inlineStr">
+        <is>
+          <t>半导体设备ETF招商</t>
+        </is>
+      </c>
+      <c r="E621" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F621" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G621" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H621" s="2" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="I621" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J621" s="2" t="n">
+        <v>6940</v>
+      </c>
+      <c r="K621" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L621" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M621" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N621" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O621" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P621" s="5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q621" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B622" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C622" s="3" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D622" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E622" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F622" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G622" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="H622" s="2" t="n">
+        <v>256.74</v>
+      </c>
+      <c r="I622" s="2" t="n">
+        <v>262.235</v>
+      </c>
+      <c r="J622" s="2" t="n">
+        <v>102696</v>
+      </c>
+      <c r="K622" s="2" t="n">
+        <v>104894</v>
+      </c>
+      <c r="L622" s="4" t="n">
+        <v>2198</v>
+      </c>
+      <c r="M622" s="2" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="N622" s="2" t="n">
+        <v>52.45</v>
+      </c>
+      <c r="O622" s="2" t="n">
+        <v>73.20999999999999</v>
+      </c>
+      <c r="P622" s="4" t="n">
+        <v>2124.79</v>
+      </c>
+      <c r="Q622" s="2" t="inlineStr">
+        <is>
+          <t>2.07%</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B623" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C623" s="3" t="inlineStr">
+        <is>
+          <t>688127</t>
+        </is>
+      </c>
+      <c r="D623" s="2" t="inlineStr">
+        <is>
+          <t>蓝特光学</t>
+        </is>
+      </c>
+      <c r="E623" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F623" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G623" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H623" s="2" t="n">
+        <v>69.51000000000001</v>
+      </c>
+      <c r="I623" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J623" s="2" t="n">
+        <v>13902</v>
+      </c>
+      <c r="K623" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L623" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M623" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N623" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O623" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P623" s="5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q623" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B624" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C624" s="3" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
+      </c>
+      <c r="D624" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="E624" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F624" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G624" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H624" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I624" s="2" t="n">
+        <v>302.6</v>
+      </c>
+      <c r="J624" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K624" s="2" t="n">
+        <v>30260</v>
+      </c>
+      <c r="L624" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M624" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N624" s="2" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="O624" s="2" t="n">
+        <v>20.13</v>
+      </c>
+      <c r="P624" s="5" t="n">
+        <v>-20.13</v>
+      </c>
+      <c r="Q624" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="股票盈亏汇总" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="股票盈亏汇总" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q624"/>
+  <dimension ref="A1:Q634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -39805,6 +39805,636 @@
         </is>
       </c>
     </row>
+    <row r="625">
+      <c r="A625" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B625" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C625" s="3" t="inlineStr">
+        <is>
+          <t>688008</t>
+        </is>
+      </c>
+      <c r="D625" s="2" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="E625" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F625" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G625" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H625" s="2" t="n">
+        <v>224.16</v>
+      </c>
+      <c r="I625" s="2" t="n">
+        <v>225.49</v>
+      </c>
+      <c r="J625" s="2" t="n">
+        <v>44832</v>
+      </c>
+      <c r="K625" s="2" t="n">
+        <v>45098</v>
+      </c>
+      <c r="L625" s="4" t="n">
+        <v>266</v>
+      </c>
+      <c r="M625" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N625" s="2" t="n">
+        <v>22.55</v>
+      </c>
+      <c r="O625" s="2" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="P625" s="4" t="n">
+        <v>233.45</v>
+      </c>
+      <c r="Q625" s="2" t="inlineStr">
+        <is>
+          <t>0.52%</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B626" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C626" s="3" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D626" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E626" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F626" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G626" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H626" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I626" s="2" t="n">
+        <v>46.04</v>
+      </c>
+      <c r="J626" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K626" s="2" t="n">
+        <v>9208</v>
+      </c>
+      <c r="L626" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M626" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N626" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O626" s="2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="P626" s="5" t="n">
+        <v>-9.6</v>
+      </c>
+      <c r="Q626" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B627" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C627" s="3" t="inlineStr">
+        <is>
+          <t>688603</t>
+        </is>
+      </c>
+      <c r="D627" s="2" t="inlineStr">
+        <is>
+          <t>天承科技</t>
+        </is>
+      </c>
+      <c r="E627" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F627" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="G627" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H627" s="2" t="n">
+        <v>124.65</v>
+      </c>
+      <c r="I627" s="2" t="n">
+        <v>126.6</v>
+      </c>
+      <c r="J627" s="2" t="n">
+        <v>12465</v>
+      </c>
+      <c r="K627" s="2" t="n">
+        <v>12660</v>
+      </c>
+      <c r="L627" s="4" t="n">
+        <v>195</v>
+      </c>
+      <c r="M627" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N627" s="2" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="O627" s="2" t="n">
+        <v>16.33</v>
+      </c>
+      <c r="P627" s="4" t="n">
+        <v>178.67</v>
+      </c>
+      <c r="Q627" s="2" t="inlineStr">
+        <is>
+          <t>1.43%</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B628" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C628" s="3" t="inlineStr">
+        <is>
+          <t>688603</t>
+        </is>
+      </c>
+      <c r="D628" s="2" t="inlineStr">
+        <is>
+          <t>天承科技</t>
+        </is>
+      </c>
+      <c r="E628" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F628" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G628" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H628" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I628" s="2" t="n">
+        <v>126.6</v>
+      </c>
+      <c r="J628" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K628" s="2" t="n">
+        <v>7722.6</v>
+      </c>
+      <c r="L628" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M628" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N628" s="2" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="O628" s="2" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="P628" s="5" t="n">
+        <v>-8.859999999999999</v>
+      </c>
+      <c r="Q628" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多卖未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B629" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C629" s="3" t="inlineStr">
+        <is>
+          <t>002222</t>
+        </is>
+      </c>
+      <c r="D629" s="2" t="inlineStr">
+        <is>
+          <t>福晶科技</t>
+        </is>
+      </c>
+      <c r="E629" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F629" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G629" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H629" s="2" t="n">
+        <v>70.02</v>
+      </c>
+      <c r="I629" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J629" s="2" t="n">
+        <v>21006</v>
+      </c>
+      <c r="K629" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L629" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M629" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N629" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O629" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P629" s="5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q629" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B630" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C630" s="3" t="inlineStr">
+        <is>
+          <t>300750</t>
+        </is>
+      </c>
+      <c r="D630" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代</t>
+        </is>
+      </c>
+      <c r="E630" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F630" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G630" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H630" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I630" s="2" t="n">
+        <v>299.9</v>
+      </c>
+      <c r="J630" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K630" s="2" t="n">
+        <v>29990</v>
+      </c>
+      <c r="L630" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M630" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N630" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="O630" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="P630" s="5" t="n">
+        <v>-20</v>
+      </c>
+      <c r="Q630" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B631" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C631" s="3" t="inlineStr">
+        <is>
+          <t>002837</t>
+        </is>
+      </c>
+      <c r="D631" s="2" t="inlineStr">
+        <is>
+          <t>英维克</t>
+        </is>
+      </c>
+      <c r="E631" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F631" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G631" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H631" s="2" t="n">
+        <v>61.17</v>
+      </c>
+      <c r="I631" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J631" s="2" t="n">
+        <v>18351</v>
+      </c>
+      <c r="K631" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L631" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M631" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N631" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O631" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P631" s="5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q631" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B632" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C632" s="3" t="inlineStr">
+        <is>
+          <t>603228</t>
+        </is>
+      </c>
+      <c r="D632" s="2" t="inlineStr">
+        <is>
+          <t>景旺电子</t>
+        </is>
+      </c>
+      <c r="E632" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="F632" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G632" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H632" s="2" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="I632" s="2" t="n">
+        <v>110.33</v>
+      </c>
+      <c r="J632" s="2" t="n">
+        <v>10910</v>
+      </c>
+      <c r="K632" s="2" t="n">
+        <v>11033</v>
+      </c>
+      <c r="L632" s="4" t="n">
+        <v>123</v>
+      </c>
+      <c r="M632" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N632" s="2" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="O632" s="2" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="P632" s="4" t="n">
+        <v>107.48</v>
+      </c>
+      <c r="Q632" s="2" t="inlineStr">
+        <is>
+          <t>0.99%</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B633" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C633" s="3" t="inlineStr">
+        <is>
+          <t>603228</t>
+        </is>
+      </c>
+      <c r="D633" s="2" t="inlineStr">
+        <is>
+          <t>景旺电子</t>
+        </is>
+      </c>
+      <c r="E633" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F633" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G633" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H633" s="2" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="I633" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J633" s="2" t="n">
+        <v>21820</v>
+      </c>
+      <c r="K633" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L633" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M633" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N633" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O633" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P633" s="5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q633" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B634" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+平安账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C634" s="3" t="inlineStr">
+        <is>
+          <t>600127</t>
+        </is>
+      </c>
+      <c r="D634" s="2" t="inlineStr">
+        <is>
+          <t>金健米业</t>
+        </is>
+      </c>
+      <c r="E634" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F634" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="G634" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H634" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I634" s="2" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="J634" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K634" s="2" t="n">
+        <v>8205</v>
+      </c>
+      <c r="L634" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M634" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N634" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O634" s="2" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="P634" s="5" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="Q634" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅卖出未平仓</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q634"/>
+  <dimension ref="A1:Q640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -40435,6 +40435,384 @@
         </is>
       </c>
     </row>
+    <row r="635">
+      <c r="A635" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B635" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C635" s="3" t="inlineStr">
+        <is>
+          <t>688127</t>
+        </is>
+      </c>
+      <c r="D635" s="2" t="inlineStr">
+        <is>
+          <t>蓝特光学</t>
+        </is>
+      </c>
+      <c r="E635" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F635" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G635" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H635" s="2" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="I635" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J635" s="2" t="n">
+        <v>26640</v>
+      </c>
+      <c r="K635" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L635" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M635" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N635" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O635" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P635" s="5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q635" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B636" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C636" s="3" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D636" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E636" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F636" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G636" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H636" s="2" t="n">
+        <v>248.735</v>
+      </c>
+      <c r="I636" s="2" t="n">
+        <v>250.35</v>
+      </c>
+      <c r="J636" s="2" t="n">
+        <v>49747</v>
+      </c>
+      <c r="K636" s="2" t="n">
+        <v>50070</v>
+      </c>
+      <c r="L636" s="4" t="n">
+        <v>323</v>
+      </c>
+      <c r="M636" s="2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="N636" s="2" t="n">
+        <v>25.04</v>
+      </c>
+      <c r="O636" s="2" t="n">
+        <v>35.05</v>
+      </c>
+      <c r="P636" s="4" t="n">
+        <v>287.95</v>
+      </c>
+      <c r="Q636" s="2" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B637" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C637" s="3" t="inlineStr">
+        <is>
+          <t>688041</t>
+        </is>
+      </c>
+      <c r="D637" s="2" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="E637" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F637" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G637" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H637" s="2" t="n">
+        <v>248.735</v>
+      </c>
+      <c r="I637" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J637" s="2" t="n">
+        <v>49747</v>
+      </c>
+      <c r="K637" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L637" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M637" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N637" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O637" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P637" s="5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q637" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B638" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C638" s="3" t="inlineStr">
+        <is>
+          <t>688603</t>
+        </is>
+      </c>
+      <c r="D638" s="2" t="inlineStr">
+        <is>
+          <t>天承科技</t>
+        </is>
+      </c>
+      <c r="E638" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F638" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G638" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H638" s="2" t="n">
+        <v>126.02</v>
+      </c>
+      <c r="I638" s="2" t="n">
+        <v>127.82</v>
+      </c>
+      <c r="J638" s="2" t="n">
+        <v>12602</v>
+      </c>
+      <c r="K638" s="2" t="n">
+        <v>12782</v>
+      </c>
+      <c r="L638" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="M638" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N638" s="2" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="O638" s="2" t="n">
+        <v>16.39</v>
+      </c>
+      <c r="P638" s="4" t="n">
+        <v>163.61</v>
+      </c>
+      <c r="Q638" s="2" t="inlineStr">
+        <is>
+          <t>1.30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B639" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C639" s="3" t="inlineStr">
+        <is>
+          <t>688603</t>
+        </is>
+      </c>
+      <c r="D639" s="2" t="inlineStr">
+        <is>
+          <t>天承科技</t>
+        </is>
+      </c>
+      <c r="E639" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F639" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G639" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H639" s="2" t="n">
+        <v>126.02</v>
+      </c>
+      <c r="I639" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J639" s="2" t="n">
+        <v>12602</v>
+      </c>
+      <c r="K639" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L639" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M639" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N639" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O639" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P639" s="5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q639" s="2" t="inlineStr">
+        <is>
+          <t>⚠️多买未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B640" s="2" t="inlineStr">
+        <is>
+          <t>两融账户+手机账户</t>
+        </is>
+      </c>
+      <c r="C640" s="3" t="inlineStr">
+        <is>
+          <t>002436</t>
+        </is>
+      </c>
+      <c r="D640" s="2" t="inlineStr">
+        <is>
+          <t>兴森科技</t>
+        </is>
+      </c>
+      <c r="E640" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F640" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G640" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H640" s="2" t="n">
+        <v>43.71</v>
+      </c>
+      <c r="I640" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J640" s="2" t="n">
+        <v>21855</v>
+      </c>
+      <c r="K640" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L640" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M640" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N640" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O640" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P640" s="5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q640" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>200</v>
@@ -959,7 +959,7 @@
         <v>200</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>200</v>
@@ -1022,7 +1022,7 @@
         <v>112</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>200</v>
+        <v>112</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>112</v>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>100</v>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>200</v>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>200</v>
@@ -2345,7 +2345,7 @@
         <v>100</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>100</v>
@@ -2471,7 +2471,7 @@
         <v>900</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>900</v>
@@ -2786,7 +2786,7 @@
         <v>600</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>600</v>
@@ -2849,7 +2849,7 @@
         <v>100</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>100</v>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>400</v>
+        <v>119</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>119</v>
@@ -3416,7 +3416,7 @@
         <v>200</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>481</v>
+        <v>200</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>200</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>432</v>
+        <v>132</v>
       </c>
       <c r="F48" s="2" t="n">
         <v>132</v>
@@ -4865,7 +4865,7 @@
         <v>100</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>100</v>
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F75" s="2" t="n">
         <v>100</v>
@@ -6188,7 +6188,7 @@
         <v>400</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="G91" s="2" t="n">
         <v>400</v>
@@ -6314,7 +6314,7 @@
         <v>100</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G93" s="2" t="n">
         <v>100</v>
@@ -6752,7 +6752,7 @@
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="F100" s="2" t="n">
         <v>500</v>
@@ -7130,7 +7130,7 @@
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F106" s="2" t="n">
         <v>300</v>
@@ -7508,7 +7508,7 @@
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="F112" s="2" t="n">
         <v>400</v>
@@ -8264,7 +8264,7 @@
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F124" s="2" t="n">
         <v>200</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="E127" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F127" s="2" t="n">
         <v>100</v>
@@ -8834,7 +8834,7 @@
         <v>200</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G133" s="2" t="n">
         <v>200</v>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="E136" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F136" s="2" t="n">
         <v>200</v>
@@ -9335,7 +9335,7 @@
         </is>
       </c>
       <c r="E141" s="2" t="n">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="F141" s="2" t="n">
         <v>400</v>
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="E150" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F150" s="2" t="n">
         <v>200</v>
@@ -10217,7 +10217,7 @@
         </is>
       </c>
       <c r="E155" s="2" t="n">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="F155" s="2" t="n">
         <v>600</v>
@@ -10346,7 +10346,7 @@
         <v>200</v>
       </c>
       <c r="F157" s="2" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G157" s="2" t="n">
         <v>200</v>
@@ -11354,7 +11354,7 @@
         <v>300</v>
       </c>
       <c r="F173" s="2" t="n">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="G173" s="2" t="n">
         <v>300</v>
@@ -11540,7 +11540,7 @@
         </is>
       </c>
       <c r="E176" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F176" s="2" t="n">
         <v>200</v>
@@ -11918,7 +11918,7 @@
         </is>
       </c>
       <c r="E182" s="2" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="F182" s="2" t="n">
         <v>200</v>
@@ -12866,7 +12866,7 @@
         <v>100</v>
       </c>
       <c r="F197" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G197" s="2" t="n">
         <v>100</v>
@@ -13181,7 +13181,7 @@
         <v>200</v>
       </c>
       <c r="F202" s="2" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="G202" s="2" t="n">
         <v>200</v>
@@ -14126,7 +14126,7 @@
         <v>500</v>
       </c>
       <c r="F217" s="2" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="G217" s="2" t="n">
         <v>500</v>
@@ -14378,7 +14378,7 @@
         <v>100</v>
       </c>
       <c r="F221" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G221" s="2" t="n">
         <v>100</v>
@@ -15446,7 +15446,7 @@
         </is>
       </c>
       <c r="E238" s="2" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="F238" s="2" t="n">
         <v>500</v>
@@ -15572,7 +15572,7 @@
         </is>
       </c>
       <c r="E240" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F240" s="2" t="n">
         <v>200</v>
@@ -16013,7 +16013,7 @@
         </is>
       </c>
       <c r="E247" s="2" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="F247" s="2" t="n">
         <v>300</v>
@@ -16457,7 +16457,7 @@
         <v>500</v>
       </c>
       <c r="F254" s="2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="G254" s="2" t="n">
         <v>500</v>
@@ -16961,7 +16961,7 @@
         <v>200</v>
       </c>
       <c r="F262" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G262" s="2" t="n">
         <v>200</v>
@@ -17336,7 +17336,7 @@
         </is>
       </c>
       <c r="E268" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F268" s="2" t="n">
         <v>100</v>
@@ -17969,7 +17969,7 @@
         <v>200</v>
       </c>
       <c r="F278" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G278" s="2" t="n">
         <v>200</v>
@@ -18725,7 +18725,7 @@
         <v>100</v>
       </c>
       <c r="F290" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G290" s="2" t="n">
         <v>100</v>
@@ -18911,7 +18911,7 @@
         </is>
       </c>
       <c r="E293" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F293" s="2" t="n">
         <v>200</v>
@@ -19415,7 +19415,7 @@
         </is>
       </c>
       <c r="E301" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F301" s="2" t="n">
         <v>100</v>
@@ -19544,7 +19544,7 @@
         <v>100</v>
       </c>
       <c r="F303" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G303" s="2" t="n">
         <v>100</v>
@@ -19730,7 +19730,7 @@
         </is>
       </c>
       <c r="E306" s="2" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="F306" s="2" t="n">
         <v>600</v>
@@ -19922,7 +19922,7 @@
         <v>100</v>
       </c>
       <c r="F309" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G309" s="2" t="n">
         <v>100</v>
@@ -20108,7 +20108,7 @@
         </is>
       </c>
       <c r="E312" s="2" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F312" s="2" t="n">
         <v>200</v>
@@ -20423,7 +20423,7 @@
         </is>
       </c>
       <c r="E317" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F317" s="2" t="n">
         <v>200</v>
@@ -20804,7 +20804,7 @@
         <v>400</v>
       </c>
       <c r="F323" s="2" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="G323" s="2" t="n">
         <v>400</v>
@@ -20930,7 +20930,7 @@
         <v>100</v>
       </c>
       <c r="F325" s="2" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="G325" s="2" t="n">
         <v>100</v>
@@ -21620,7 +21620,7 @@
         </is>
       </c>
       <c r="E336" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F336" s="2" t="n">
         <v>100</v>
@@ -22064,7 +22064,7 @@
         <v>200</v>
       </c>
       <c r="F343" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G343" s="2" t="n">
         <v>200</v>
@@ -22253,7 +22253,7 @@
         <v>200</v>
       </c>
       <c r="F346" s="2" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G346" s="2" t="n">
         <v>200</v>
@@ -22631,7 +22631,7 @@
         <v>100</v>
       </c>
       <c r="F352" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G352" s="2" t="n">
         <v>100</v>
@@ -23639,7 +23639,7 @@
         <v>400</v>
       </c>
       <c r="F368" s="2" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="G368" s="2" t="n">
         <v>400</v>
@@ -23891,7 +23891,7 @@
         <v>200</v>
       </c>
       <c r="F372" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G372" s="2" t="n">
         <v>200</v>
@@ -24581,7 +24581,7 @@
         </is>
       </c>
       <c r="E383" s="2" t="n">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="F383" s="2" t="n">
         <v>900</v>
@@ -24770,7 +24770,7 @@
         </is>
       </c>
       <c r="E386" s="2" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="F386" s="2" t="n">
         <v>500</v>
@@ -24896,7 +24896,7 @@
         </is>
       </c>
       <c r="E388" s="2" t="n">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="F388" s="2" t="n">
         <v>500</v>
@@ -25088,7 +25088,7 @@
         <v>600</v>
       </c>
       <c r="F391" s="2" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G391" s="2" t="n">
         <v>600</v>
@@ -25211,7 +25211,7 @@
         </is>
       </c>
       <c r="E393" s="2" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="F393" s="2" t="n">
         <v>600</v>
@@ -25592,7 +25592,7 @@
         <v>1400</v>
       </c>
       <c r="F399" s="2" t="n">
-        <v>1800</v>
+        <v>1400</v>
       </c>
       <c r="G399" s="2" t="n">
         <v>1400</v>
@@ -25781,7 +25781,7 @@
         <v>600</v>
       </c>
       <c r="F402" s="2" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="G402" s="2" t="n">
         <v>600</v>
@@ -25970,7 +25970,7 @@
         <v>400</v>
       </c>
       <c r="F405" s="2" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="G405" s="2" t="n">
         <v>400</v>
@@ -26408,7 +26408,7 @@
         </is>
       </c>
       <c r="E412" s="2" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F412" s="2" t="n">
         <v>200</v>
@@ -26663,7 +26663,7 @@
         <v>100</v>
       </c>
       <c r="F416" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G416" s="2" t="n">
         <v>100</v>
@@ -26786,7 +26786,7 @@
         </is>
       </c>
       <c r="E418" s="2" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F418" s="2" t="n">
         <v>400</v>
@@ -27419,7 +27419,7 @@
         <v>200</v>
       </c>
       <c r="F428" s="2" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G428" s="2" t="n">
         <v>200</v>
@@ -27923,7 +27923,7 @@
         <v>400</v>
       </c>
       <c r="F436" s="2" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="G436" s="2" t="n">
         <v>400</v>
@@ -28238,7 +28238,7 @@
         <v>200</v>
       </c>
       <c r="F441" s="2" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="G441" s="2" t="n">
         <v>200</v>
@@ -28364,7 +28364,7 @@
         <v>100</v>
       </c>
       <c r="F443" s="2" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G443" s="2" t="n">
         <v>100</v>
@@ -28487,7 +28487,7 @@
         </is>
       </c>
       <c r="E445" s="2" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="F445" s="2" t="n">
         <v>600</v>
@@ -29057,7 +29057,7 @@
         <v>200</v>
       </c>
       <c r="F454" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G454" s="2" t="n">
         <v>200</v>
@@ -30125,7 +30125,7 @@
         </is>
       </c>
       <c r="E471" s="2" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="F471" s="2" t="n">
         <v>200</v>
@@ -30254,7 +30254,7 @@
         <v>400</v>
       </c>
       <c r="F473" s="2" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="G473" s="2" t="n">
         <v>400</v>
@@ -30881,7 +30881,7 @@
         </is>
       </c>
       <c r="E483" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F483" s="2" t="n">
         <v>200</v>
@@ -31514,7 +31514,7 @@
         <v>200</v>
       </c>
       <c r="F493" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G493" s="2" t="n">
         <v>200</v>
@@ -31826,7 +31826,7 @@
         </is>
       </c>
       <c r="E498" s="2" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="F498" s="2" t="n">
         <v>3000</v>
@@ -31952,7 +31952,7 @@
         </is>
       </c>
       <c r="E500" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F500" s="2" t="n">
         <v>200</v>
@@ -32897,7 +32897,7 @@
         </is>
       </c>
       <c r="E515" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F515" s="2" t="n">
         <v>200</v>
@@ -34220,7 +34220,7 @@
         </is>
       </c>
       <c r="E536" s="2" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="F536" s="2" t="n">
         <v>600</v>
@@ -36680,7 +36680,7 @@
         <v>1000</v>
       </c>
       <c r="F575" s="2" t="n">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="G575" s="2" t="n">
         <v>1000</v>
@@ -36929,7 +36929,7 @@
         </is>
       </c>
       <c r="E579" s="2" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="F579" s="2" t="n">
         <v>800</v>
@@ -38696,7 +38696,7 @@
         <v>400</v>
       </c>
       <c r="F607" s="2" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="G607" s="2" t="n">
         <v>400</v>
@@ -38885,7 +38885,7 @@
         <v>200</v>
       </c>
       <c r="F610" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G610" s="2" t="n">
         <v>200</v>
@@ -39197,7 +39197,7 @@
         </is>
       </c>
       <c r="E615" s="2" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="F615" s="2" t="n">
         <v>200</v>
@@ -39956,7 +39956,7 @@
         <v>100</v>
       </c>
       <c r="F627" s="2" t="n">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="G627" s="2" t="n">
         <v>100</v>
@@ -40268,7 +40268,7 @@
         </is>
       </c>
       <c r="E632" s="2" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F632" s="2" t="n">
         <v>100</v>
@@ -40448,16 +40448,16 @@
       </c>
       <c r="C635" s="3" t="inlineStr">
         <is>
-          <t>688127</t>
+          <t>002436</t>
         </is>
       </c>
       <c r="D635" s="2" t="inlineStr">
         <is>
-          <t>蓝特光学</t>
+          <t>兴森科技</t>
         </is>
       </c>
       <c r="E635" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="F635" s="2" t="n">
         <v>0</v>
@@ -40466,13 +40466,13 @@
         <v>0</v>
       </c>
       <c r="H635" s="2" t="n">
-        <v>66.59999999999999</v>
+        <v>43.71</v>
       </c>
       <c r="I635" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J635" s="2" t="n">
-        <v>26640</v>
+        <v>21855</v>
       </c>
       <c r="K635" s="2" t="n">
         <v>0</v>
@@ -40511,53 +40511,53 @@
       </c>
       <c r="C636" s="3" t="inlineStr">
         <is>
-          <t>688041</t>
+          <t>688127</t>
         </is>
       </c>
       <c r="D636" s="2" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>蓝特光学</t>
         </is>
       </c>
       <c r="E636" s="2" t="n">
         <v>400</v>
       </c>
       <c r="F636" s="2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G636" s="2" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H636" s="2" t="n">
-        <v>248.735</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I636" s="2" t="n">
-        <v>250.35</v>
+        <v>0</v>
       </c>
       <c r="J636" s="2" t="n">
-        <v>49747</v>
+        <v>26640</v>
       </c>
       <c r="K636" s="2" t="n">
-        <v>50070</v>
-      </c>
-      <c r="L636" s="4" t="n">
-        <v>323</v>
+        <v>0</v>
+      </c>
+      <c r="L636" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="M636" s="2" t="n">
-        <v>10.01</v>
+        <v>5</v>
       </c>
       <c r="N636" s="2" t="n">
-        <v>25.04</v>
+        <v>0</v>
       </c>
       <c r="O636" s="2" t="n">
-        <v>35.05</v>
-      </c>
-      <c r="P636" s="4" t="n">
-        <v>287.95</v>
+        <v>5</v>
+      </c>
+      <c r="P636" s="5" t="n">
+        <v>-5</v>
       </c>
       <c r="Q636" s="2" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>⚠️仅买入未平仓</t>
         </is>
       </c>
     </row>
@@ -40586,41 +40586,41 @@
         <v>200</v>
       </c>
       <c r="F637" s="2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G637" s="2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H637" s="2" t="n">
         <v>248.735</v>
       </c>
       <c r="I637" s="2" t="n">
-        <v>0</v>
+        <v>250.35</v>
       </c>
       <c r="J637" s="2" t="n">
         <v>49747</v>
       </c>
       <c r="K637" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L637" s="5" t="n">
-        <v>0</v>
+        <v>50070</v>
+      </c>
+      <c r="L637" s="4" t="n">
+        <v>323</v>
       </c>
       <c r="M637" s="2" t="n">
-        <v>5</v>
+        <v>10.01</v>
       </c>
       <c r="N637" s="2" t="n">
-        <v>0</v>
+        <v>25.04</v>
       </c>
       <c r="O637" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="P637" s="5" t="n">
-        <v>-5</v>
+        <v>35.05</v>
+      </c>
+      <c r="P637" s="4" t="n">
+        <v>287.95</v>
       </c>
       <c r="Q637" s="2" t="inlineStr">
         <is>
-          <t>⚠️多买未平仓</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -40637,53 +40637,53 @@
       </c>
       <c r="C638" s="3" t="inlineStr">
         <is>
-          <t>688603</t>
+          <t>688041</t>
         </is>
       </c>
       <c r="D638" s="2" t="inlineStr">
         <is>
-          <t>天承科技</t>
+          <t>海光信息</t>
         </is>
       </c>
       <c r="E638" s="2" t="n">
         <v>200</v>
       </c>
       <c r="F638" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G638" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H638" s="2" t="n">
-        <v>126.02</v>
+        <v>248.735</v>
       </c>
       <c r="I638" s="2" t="n">
-        <v>127.82</v>
+        <v>0</v>
       </c>
       <c r="J638" s="2" t="n">
-        <v>12602</v>
+        <v>49747</v>
       </c>
       <c r="K638" s="2" t="n">
-        <v>12782</v>
-      </c>
-      <c r="L638" s="4" t="n">
-        <v>180</v>
+        <v>0</v>
+      </c>
+      <c r="L638" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="M638" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N638" s="2" t="n">
-        <v>6.39</v>
+        <v>0</v>
       </c>
       <c r="O638" s="2" t="n">
-        <v>16.39</v>
-      </c>
-      <c r="P638" s="4" t="n">
-        <v>163.61</v>
+        <v>5</v>
+      </c>
+      <c r="P638" s="5" t="n">
+        <v>-5</v>
       </c>
       <c r="Q638" s="2" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>⚠️多买未平仓</t>
         </is>
       </c>
     </row>
@@ -40712,41 +40712,41 @@
         <v>100</v>
       </c>
       <c r="F639" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G639" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H639" s="2" t="n">
         <v>126.02</v>
       </c>
       <c r="I639" s="2" t="n">
-        <v>0</v>
+        <v>127.82</v>
       </c>
       <c r="J639" s="2" t="n">
         <v>12602</v>
       </c>
       <c r="K639" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L639" s="5" t="n">
-        <v>0</v>
+        <v>12782</v>
+      </c>
+      <c r="L639" s="4" t="n">
+        <v>180</v>
       </c>
       <c r="M639" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N639" s="2" t="n">
-        <v>0</v>
+        <v>6.39</v>
       </c>
       <c r="O639" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="P639" s="5" t="n">
-        <v>-5</v>
+        <v>16.39</v>
+      </c>
+      <c r="P639" s="4" t="n">
+        <v>163.61</v>
       </c>
       <c r="Q639" s="2" t="inlineStr">
         <is>
-          <t>⚠️多买未平仓</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
@@ -40763,16 +40763,16 @@
       </c>
       <c r="C640" s="3" t="inlineStr">
         <is>
-          <t>002436</t>
+          <t>688603</t>
         </is>
       </c>
       <c r="D640" s="2" t="inlineStr">
         <is>
-          <t>兴森科技</t>
+          <t>天承科技</t>
         </is>
       </c>
       <c r="E640" s="2" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F640" s="2" t="n">
         <v>0</v>
@@ -40781,13 +40781,13 @@
         <v>0</v>
       </c>
       <c r="H640" s="2" t="n">
-        <v>43.71</v>
+        <v>126.02</v>
       </c>
       <c r="I640" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J640" s="2" t="n">
-        <v>21855</v>
+        <v>12602</v>
       </c>
       <c r="K640" s="2" t="n">
         <v>0</v>
@@ -40809,7 +40809,7 @@
       </c>
       <c r="Q640" s="2" t="inlineStr">
         <is>
-          <t>⚠️仅买入未平仓</t>
+          <t>⚠️多买未平仓</t>
         </is>
       </c>
     </row>

--- a/股票交易盈亏汇总.xlsx
+++ b/股票交易盈亏汇总.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q640"/>
+  <dimension ref="A1:Q642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -40813,6 +40813,132 @@
         </is>
       </c>
     </row>
+    <row r="641">
+      <c r="A641" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B641" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C641" s="3" t="inlineStr">
+        <is>
+          <t>688127</t>
+        </is>
+      </c>
+      <c r="D641" s="2" t="inlineStr">
+        <is>
+          <t>蓝特光学</t>
+        </is>
+      </c>
+      <c r="E641" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F641" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G641" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H641" s="2" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="I641" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J641" s="2" t="n">
+        <v>12580</v>
+      </c>
+      <c r="K641" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L641" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M641" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N641" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O641" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P641" s="5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q641" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B642" s="2" t="inlineStr">
+        <is>
+          <t>两融账户</t>
+        </is>
+      </c>
+      <c r="C642" s="3" t="inlineStr">
+        <is>
+          <t>688603</t>
+        </is>
+      </c>
+      <c r="D642" s="2" t="inlineStr">
+        <is>
+          <t>天承科技</t>
+        </is>
+      </c>
+      <c r="E642" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="F642" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G642" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H642" s="2" t="n">
+        <v>117.02</v>
+      </c>
+      <c r="I642" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J642" s="2" t="n">
+        <v>23404</v>
+      </c>
+      <c r="K642" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L642" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M642" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N642" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O642" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P642" s="5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q642" s="2" t="inlineStr">
+        <is>
+          <t>⚠️仅买入未平仓</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
